--- a/pruebasics.xlsx
+++ b/pruebasics.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B65E7D8-DAE0-4AE7-9BBE-F65FAEB390D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1E2937B-C84E-4C23-B7FE-41CD1F9DECD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{683E6D3C-622D-40B0-99F3-294855D410CE}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$668</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="14">
+  <si>
+    <t>lote</t>
+  </si>
+  <si>
+    <t>mes</t>
+  </si>
+  <si>
+    <t>dia</t>
+  </si>
+  <si>
+    <t>Consumo agua recuperada</t>
+  </si>
+  <si>
+    <t>Consumo agua potable</t>
+  </si>
+  <si>
+    <t>Malta en germen</t>
+  </si>
+  <si>
+    <t>Pasamalla Cebada</t>
+  </si>
+  <si>
+    <t>Pasamalla Malta</t>
+  </si>
   <si>
     <t>Dec</t>
   </si>
@@ -60,30 +84,6 @@
   </si>
   <si>
     <t>May</t>
-  </si>
-  <si>
-    <t>mes</t>
-  </si>
-  <si>
-    <t>lote</t>
-  </si>
-  <si>
-    <t>dia</t>
-  </si>
-  <si>
-    <t>Consumo agua recuperada</t>
-  </si>
-  <si>
-    <t>Consumo agua potable</t>
-  </si>
-  <si>
-    <t>Pasamalla Malta</t>
-  </si>
-  <si>
-    <t>Pasamalla Cebada</t>
-  </si>
-  <si>
-    <t>Malta en germen</t>
   </si>
 </sst>
 </file>
@@ -455,33 +455,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6A4A6A-BD55-4AFD-8065-F1F24C71989F}">
-  <dimension ref="A1:H668"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H717"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -489,7 +489,7 @@
         <v>26743</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>25</v>
@@ -515,7 +515,7 @@
         <v>26744</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -541,7 +541,7 @@
         <v>26745</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>25</v>
@@ -567,7 +567,7 @@
         <v>26746</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>25</v>
@@ -593,7 +593,7 @@
         <v>26747</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>25</v>
@@ -619,7 +619,7 @@
         <v>26748</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -645,7 +645,7 @@
         <v>26749</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>26</v>
@@ -671,7 +671,7 @@
         <v>26750</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>26</v>
@@ -697,7 +697,7 @@
         <v>26751</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>26</v>
@@ -723,7 +723,7 @@
         <v>26752</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>26</v>
@@ -749,7 +749,7 @@
         <v>26753</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>26</v>
@@ -775,7 +775,7 @@
         <v>26754</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>27</v>
@@ -801,7 +801,7 @@
         <v>26755</v>
       </c>
       <c r="B14" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>27</v>
@@ -827,7 +827,7 @@
         <v>26756</v>
       </c>
       <c r="B15" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>27</v>
@@ -853,7 +853,7 @@
         <v>26757</v>
       </c>
       <c r="B16" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>27</v>
@@ -879,7 +879,7 @@
         <v>26758</v>
       </c>
       <c r="B17" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>27</v>
@@ -905,7 +905,7 @@
         <v>26759</v>
       </c>
       <c r="B18" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C18">
         <v>28</v>
@@ -931,7 +931,7 @@
         <v>26760</v>
       </c>
       <c r="B19" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>28</v>
@@ -957,7 +957,7 @@
         <v>26761</v>
       </c>
       <c r="B20" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>28</v>
@@ -983,7 +983,7 @@
         <v>26762</v>
       </c>
       <c r="B21" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>28</v>
@@ -1009,7 +1009,7 @@
         <v>26763</v>
       </c>
       <c r="B22" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>28</v>
@@ -1035,7 +1035,7 @@
         <v>26764</v>
       </c>
       <c r="B23" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>28</v>
@@ -1061,7 +1061,7 @@
         <v>26765</v>
       </c>
       <c r="B24" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C24">
         <v>29</v>
@@ -1087,7 +1087,7 @@
         <v>26766</v>
       </c>
       <c r="B25" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>29</v>
@@ -1113,7 +1113,7 @@
         <v>26767</v>
       </c>
       <c r="B26" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>29</v>
@@ -1139,7 +1139,7 @@
         <v>26768</v>
       </c>
       <c r="B27" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C27">
         <v>29</v>
@@ -1165,7 +1165,7 @@
         <v>26769</v>
       </c>
       <c r="B28" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -1191,7 +1191,7 @@
         <v>26770</v>
       </c>
       <c r="B29" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -1217,7 +1217,7 @@
         <v>26771</v>
       </c>
       <c r="B30" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -1243,7 +1243,7 @@
         <v>26772</v>
       </c>
       <c r="B31" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1269,7 +1269,7 @@
         <v>26773</v>
       </c>
       <c r="B32" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>30</v>
@@ -1295,7 +1295,7 @@
         <v>26774</v>
       </c>
       <c r="B33" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C33">
         <v>31</v>
@@ -1321,7 +1321,7 @@
         <v>26775</v>
       </c>
       <c r="B34" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C34">
         <v>31</v>
@@ -1347,7 +1347,7 @@
         <v>26776</v>
       </c>
       <c r="B35" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>31</v>
@@ -1373,7 +1373,7 @@
         <v>26777</v>
       </c>
       <c r="B36" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C36">
         <v>31</v>
@@ -1399,7 +1399,7 @@
         <v>26778</v>
       </c>
       <c r="B37" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C37">
         <v>31</v>
@@ -1425,7 +1425,7 @@
         <v>26779</v>
       </c>
       <c r="B38" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C38">
         <v>31</v>
@@ -1451,7 +1451,7 @@
         <v>26780</v>
       </c>
       <c r="B39" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1477,7 +1477,7 @@
         <v>26781</v>
       </c>
       <c r="B40" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1503,7 +1503,7 @@
         <v>26782</v>
       </c>
       <c r="B41" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1529,7 +1529,7 @@
         <v>26783</v>
       </c>
       <c r="B42" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -1555,7 +1555,7 @@
         <v>26784</v>
       </c>
       <c r="B43" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1581,7 +1581,7 @@
         <v>26785</v>
       </c>
       <c r="B44" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1607,7 +1607,7 @@
         <v>26786</v>
       </c>
       <c r="B45" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -1633,7 +1633,7 @@
         <v>26787</v>
       </c>
       <c r="B46" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -1659,7 +1659,7 @@
         <v>26788</v>
       </c>
       <c r="B47" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -1685,7 +1685,7 @@
         <v>26789</v>
       </c>
       <c r="B48" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -1711,7 +1711,7 @@
         <v>26790</v>
       </c>
       <c r="B49" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -1737,7 +1737,7 @@
         <v>26791</v>
       </c>
       <c r="B50" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -1763,7 +1763,7 @@
         <v>26792</v>
       </c>
       <c r="B51" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -1789,7 +1789,7 @@
         <v>26793</v>
       </c>
       <c r="B52" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -1815,7 +1815,7 @@
         <v>26794</v>
       </c>
       <c r="B53" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -1841,7 +1841,7 @@
         <v>26795</v>
       </c>
       <c r="B54" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C54">
         <v>4</v>
@@ -1867,7 +1867,7 @@
         <v>26796</v>
       </c>
       <c r="B55" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C55">
         <v>4</v>
@@ -1893,7 +1893,7 @@
         <v>26797</v>
       </c>
       <c r="B56" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C56">
         <v>4</v>
@@ -1919,7 +1919,7 @@
         <v>26798</v>
       </c>
       <c r="B57" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C57">
         <v>4</v>
@@ -1945,7 +1945,7 @@
         <v>26799</v>
       </c>
       <c r="B58" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C58">
         <v>4</v>
@@ -1971,7 +1971,7 @@
         <v>26800</v>
       </c>
       <c r="B59" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C59">
         <v>4</v>
@@ -1997,7 +1997,7 @@
         <v>26801</v>
       </c>
       <c r="B60" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C60">
         <v>5</v>
@@ -2023,7 +2023,7 @@
         <v>26802</v>
       </c>
       <c r="B61" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C61">
         <v>5</v>
@@ -2049,7 +2049,7 @@
         <v>26803</v>
       </c>
       <c r="B62" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C62">
         <v>5</v>
@@ -2075,7 +2075,7 @@
         <v>26804</v>
       </c>
       <c r="B63" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C63">
         <v>5</v>
@@ -2101,7 +2101,7 @@
         <v>26805</v>
       </c>
       <c r="B64" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C64">
         <v>6</v>
@@ -2127,7 +2127,7 @@
         <v>26806</v>
       </c>
       <c r="B65" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C65">
         <v>6</v>
@@ -2153,7 +2153,7 @@
         <v>26807</v>
       </c>
       <c r="B66" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C66">
         <v>6</v>
@@ -2179,7 +2179,7 @@
         <v>26808</v>
       </c>
       <c r="B67" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C67">
         <v>6</v>
@@ -2205,7 +2205,7 @@
         <v>26809</v>
       </c>
       <c r="B68" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C68">
         <v>6</v>
@@ -2231,7 +2231,7 @@
         <v>26810</v>
       </c>
       <c r="B69" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C69">
         <v>6</v>
@@ -2257,7 +2257,7 @@
         <v>26811</v>
       </c>
       <c r="B70" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C70">
         <v>7</v>
@@ -2283,7 +2283,7 @@
         <v>26812</v>
       </c>
       <c r="B71" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C71">
         <v>7</v>
@@ -2309,7 +2309,7 @@
         <v>26813</v>
       </c>
       <c r="B72" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C72">
         <v>7</v>
@@ -2335,7 +2335,7 @@
         <v>26814</v>
       </c>
       <c r="B73" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C73">
         <v>7</v>
@@ -2361,7 +2361,7 @@
         <v>26815</v>
       </c>
       <c r="B74" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C74">
         <v>7</v>
@@ -2387,7 +2387,7 @@
         <v>26816</v>
       </c>
       <c r="B75" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C75">
         <v>8</v>
@@ -2413,7 +2413,7 @@
         <v>26817</v>
       </c>
       <c r="B76" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C76">
         <v>8</v>
@@ -2439,7 +2439,7 @@
         <v>26818</v>
       </c>
       <c r="B77" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C77">
         <v>8</v>
@@ -2465,7 +2465,7 @@
         <v>26819</v>
       </c>
       <c r="B78" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C78">
         <v>8</v>
@@ -2491,7 +2491,7 @@
         <v>26820</v>
       </c>
       <c r="B79" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C79">
         <v>8</v>
@@ -2517,7 +2517,7 @@
         <v>26821</v>
       </c>
       <c r="B80" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C80">
         <v>9</v>
@@ -2543,7 +2543,7 @@
         <v>26822</v>
       </c>
       <c r="B81" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C81">
         <v>9</v>
@@ -2569,7 +2569,7 @@
         <v>26823</v>
       </c>
       <c r="B82" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C82">
         <v>9</v>
@@ -2595,7 +2595,7 @@
         <v>26824</v>
       </c>
       <c r="B83" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C83">
         <v>9</v>
@@ -2621,7 +2621,7 @@
         <v>26825</v>
       </c>
       <c r="B84" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C84">
         <v>9</v>
@@ -2647,7 +2647,7 @@
         <v>26826</v>
       </c>
       <c r="B85" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C85">
         <v>10</v>
@@ -2673,7 +2673,7 @@
         <v>26827</v>
       </c>
       <c r="B86" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C86">
         <v>10</v>
@@ -2699,7 +2699,7 @@
         <v>26828</v>
       </c>
       <c r="B87" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C87">
         <v>10</v>
@@ -2725,7 +2725,7 @@
         <v>26829</v>
       </c>
       <c r="B88" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C88">
         <v>10</v>
@@ -2751,7 +2751,7 @@
         <v>26830</v>
       </c>
       <c r="B89" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C89">
         <v>10</v>
@@ -2777,7 +2777,7 @@
         <v>26831</v>
       </c>
       <c r="B90" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C90">
         <v>11</v>
@@ -2803,7 +2803,7 @@
         <v>26832</v>
       </c>
       <c r="B91" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C91">
         <v>11</v>
@@ -2829,7 +2829,7 @@
         <v>26833</v>
       </c>
       <c r="B92" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C92">
         <v>11</v>
@@ -2855,7 +2855,7 @@
         <v>26834</v>
       </c>
       <c r="B93" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C93">
         <v>11</v>
@@ -2881,7 +2881,7 @@
         <v>26835</v>
       </c>
       <c r="B94" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C94">
         <v>11</v>
@@ -2907,7 +2907,7 @@
         <v>26836</v>
       </c>
       <c r="B95" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C95">
         <v>12</v>
@@ -2933,7 +2933,7 @@
         <v>26837</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C96">
         <v>12</v>
@@ -2959,7 +2959,7 @@
         <v>26838</v>
       </c>
       <c r="B97" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C97">
         <v>12</v>
@@ -2985,7 +2985,7 @@
         <v>26839</v>
       </c>
       <c r="B98" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C98">
         <v>12</v>
@@ -3011,7 +3011,7 @@
         <v>26840</v>
       </c>
       <c r="B99" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C99">
         <v>12</v>
@@ -3037,7 +3037,7 @@
         <v>26841</v>
       </c>
       <c r="B100" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C100">
         <v>12</v>
@@ -3063,7 +3063,7 @@
         <v>26842</v>
       </c>
       <c r="B101" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C101">
         <v>13</v>
@@ -3089,7 +3089,7 @@
         <v>26843</v>
       </c>
       <c r="B102" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C102">
         <v>13</v>
@@ -3115,7 +3115,7 @@
         <v>26844</v>
       </c>
       <c r="B103" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C103">
         <v>13</v>
@@ -3141,7 +3141,7 @@
         <v>26845</v>
       </c>
       <c r="B104" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C104">
         <v>13</v>
@@ -3167,7 +3167,7 @@
         <v>26846</v>
       </c>
       <c r="B105" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C105">
         <v>13</v>
@@ -3193,7 +3193,7 @@
         <v>26847</v>
       </c>
       <c r="B106" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C106">
         <v>14</v>
@@ -3219,7 +3219,7 @@
         <v>26848</v>
       </c>
       <c r="B107" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C107">
         <v>14</v>
@@ -3245,7 +3245,7 @@
         <v>26849</v>
       </c>
       <c r="B108" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C108">
         <v>14</v>
@@ -3271,7 +3271,7 @@
         <v>26850</v>
       </c>
       <c r="B109" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C109">
         <v>14</v>
@@ -3297,7 +3297,7 @@
         <v>26851</v>
       </c>
       <c r="B110" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C110">
         <v>14</v>
@@ -3323,7 +3323,7 @@
         <v>26852</v>
       </c>
       <c r="B111" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C111">
         <v>15</v>
@@ -3349,7 +3349,7 @@
         <v>26853</v>
       </c>
       <c r="B112" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -3375,7 +3375,7 @@
         <v>26854</v>
       </c>
       <c r="B113" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C113">
         <v>15</v>
@@ -3401,7 +3401,7 @@
         <v>26855</v>
       </c>
       <c r="B114" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C114">
         <v>15</v>
@@ -3427,7 +3427,7 @@
         <v>26856</v>
       </c>
       <c r="B115" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C115">
         <v>15</v>
@@ -3453,7 +3453,7 @@
         <v>26857</v>
       </c>
       <c r="B116" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C116">
         <v>16</v>
@@ -3479,7 +3479,7 @@
         <v>26858</v>
       </c>
       <c r="B117" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C117">
         <v>16</v>
@@ -3505,7 +3505,7 @@
         <v>26859</v>
       </c>
       <c r="B118" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C118">
         <v>16</v>
@@ -3531,7 +3531,7 @@
         <v>26860</v>
       </c>
       <c r="B119" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C119">
         <v>16</v>
@@ -3557,7 +3557,7 @@
         <v>26861</v>
       </c>
       <c r="B120" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C120">
         <v>16</v>
@@ -3583,7 +3583,7 @@
         <v>26862</v>
       </c>
       <c r="B121" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C121">
         <v>17</v>
@@ -3609,7 +3609,7 @@
         <v>26863</v>
       </c>
       <c r="B122" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C122">
         <v>17</v>
@@ -3635,7 +3635,7 @@
         <v>26864</v>
       </c>
       <c r="B123" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C123">
         <v>17</v>
@@ -3661,7 +3661,7 @@
         <v>26865</v>
       </c>
       <c r="B124" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C124">
         <v>17</v>
@@ -3687,7 +3687,7 @@
         <v>26866</v>
       </c>
       <c r="B125" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C125">
         <v>17</v>
@@ -3713,7 +3713,7 @@
         <v>26867</v>
       </c>
       <c r="B126" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C126">
         <v>18</v>
@@ -3739,7 +3739,7 @@
         <v>26868</v>
       </c>
       <c r="B127" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C127">
         <v>18</v>
@@ -3765,7 +3765,7 @@
         <v>26869</v>
       </c>
       <c r="B128" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C128">
         <v>18</v>
@@ -3791,7 +3791,7 @@
         <v>26870</v>
       </c>
       <c r="B129" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C129">
         <v>18</v>
@@ -3817,7 +3817,7 @@
         <v>26871</v>
       </c>
       <c r="B130" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C130">
         <v>18</v>
@@ -3843,7 +3843,7 @@
         <v>26872</v>
       </c>
       <c r="B131" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C131">
         <v>19</v>
@@ -3869,7 +3869,7 @@
         <v>26873</v>
       </c>
       <c r="B132" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C132">
         <v>18</v>
@@ -3895,7 +3895,7 @@
         <v>26874</v>
       </c>
       <c r="B133" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C133">
         <v>19</v>
@@ -3921,7 +3921,7 @@
         <v>26875</v>
       </c>
       <c r="B134" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C134">
         <v>19</v>
@@ -3947,7 +3947,7 @@
         <v>26876</v>
       </c>
       <c r="B135" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C135">
         <v>19</v>
@@ -3973,7 +3973,7 @@
         <v>26877</v>
       </c>
       <c r="B136" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C136">
         <v>19</v>
@@ -3999,7 +3999,7 @@
         <v>26878</v>
       </c>
       <c r="B137" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C137">
         <v>20</v>
@@ -4025,7 +4025,7 @@
         <v>26879</v>
       </c>
       <c r="B138" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C138">
         <v>20</v>
@@ -4051,7 +4051,7 @@
         <v>26880</v>
       </c>
       <c r="B139" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C139">
         <v>20</v>
@@ -4077,7 +4077,7 @@
         <v>26881</v>
       </c>
       <c r="B140" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C140">
         <v>20</v>
@@ -4103,7 +4103,7 @@
         <v>26882</v>
       </c>
       <c r="B141" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C141">
         <v>21</v>
@@ -4129,7 +4129,7 @@
         <v>26883</v>
       </c>
       <c r="B142" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C142">
         <v>21</v>
@@ -4155,7 +4155,7 @@
         <v>26884</v>
       </c>
       <c r="B143" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C143">
         <v>21</v>
@@ -4181,7 +4181,7 @@
         <v>26885</v>
       </c>
       <c r="B144" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C144">
         <v>21</v>
@@ -4207,7 +4207,7 @@
         <v>26886</v>
       </c>
       <c r="B145" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C145">
         <v>21</v>
@@ -4233,7 +4233,7 @@
         <v>26887</v>
       </c>
       <c r="B146" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C146">
         <v>21</v>
@@ -4253,7 +4253,7 @@
         <v>26888</v>
       </c>
       <c r="B147" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C147">
         <v>22</v>
@@ -4279,7 +4279,7 @@
         <v>26889</v>
       </c>
       <c r="B148" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C148">
         <v>22</v>
@@ -4305,7 +4305,7 @@
         <v>26890</v>
       </c>
       <c r="B149" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C149">
         <v>22</v>
@@ -4331,7 +4331,7 @@
         <v>26891</v>
       </c>
       <c r="B150" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C150">
         <v>22</v>
@@ -4357,7 +4357,7 @@
         <v>26892</v>
       </c>
       <c r="B151" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C151">
         <v>22</v>
@@ -4383,7 +4383,7 @@
         <v>26893</v>
       </c>
       <c r="B152" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C152">
         <v>23</v>
@@ -4409,7 +4409,7 @@
         <v>26894</v>
       </c>
       <c r="B153" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C153">
         <v>23</v>
@@ -4435,7 +4435,7 @@
         <v>26895</v>
       </c>
       <c r="B154" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C154">
         <v>23</v>
@@ -4461,7 +4461,7 @@
         <v>26896</v>
       </c>
       <c r="B155" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C155">
         <v>23</v>
@@ -4487,7 +4487,7 @@
         <v>26897</v>
       </c>
       <c r="B156" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C156">
         <v>23</v>
@@ -4513,7 +4513,7 @@
         <v>26898</v>
       </c>
       <c r="B157" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C157">
         <v>23</v>
@@ -4539,7 +4539,7 @@
         <v>26899</v>
       </c>
       <c r="B158" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C158">
         <v>24</v>
@@ -4565,7 +4565,7 @@
         <v>26900</v>
       </c>
       <c r="B159" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C159">
         <v>24</v>
@@ -4591,7 +4591,7 @@
         <v>26901</v>
       </c>
       <c r="B160" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C160">
         <v>24</v>
@@ -4617,7 +4617,7 @@
         <v>26902</v>
       </c>
       <c r="B161" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C161">
         <v>24</v>
@@ -4643,7 +4643,7 @@
         <v>26903</v>
       </c>
       <c r="B162" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C162">
         <v>25</v>
@@ -4669,7 +4669,7 @@
         <v>26904</v>
       </c>
       <c r="B163" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C163">
         <v>25</v>
@@ -4695,7 +4695,7 @@
         <v>26905</v>
       </c>
       <c r="B164" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C164">
         <v>25</v>
@@ -4721,7 +4721,7 @@
         <v>26906</v>
       </c>
       <c r="B165" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C165">
         <v>25</v>
@@ -4747,7 +4747,7 @@
         <v>26907</v>
       </c>
       <c r="B166" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C166">
         <v>25</v>
@@ -4773,7 +4773,7 @@
         <v>26908</v>
       </c>
       <c r="B167" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C167">
         <v>26</v>
@@ -4799,7 +4799,7 @@
         <v>26909</v>
       </c>
       <c r="B168" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C168">
         <v>26</v>
@@ -4825,7 +4825,7 @@
         <v>26910</v>
       </c>
       <c r="B169" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C169">
         <v>26</v>
@@ -4851,7 +4851,7 @@
         <v>26911</v>
       </c>
       <c r="B170" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C170">
         <v>26</v>
@@ -4877,7 +4877,7 @@
         <v>26912</v>
       </c>
       <c r="B171" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C171">
         <v>26</v>
@@ -4903,7 +4903,7 @@
         <v>26913</v>
       </c>
       <c r="B172" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C172">
         <v>26</v>
@@ -4929,7 +4929,7 @@
         <v>26914</v>
       </c>
       <c r="B173" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C173">
         <v>27</v>
@@ -4955,7 +4955,7 @@
         <v>26915</v>
       </c>
       <c r="B174" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C174">
         <v>27</v>
@@ -4981,7 +4981,7 @@
         <v>26916</v>
       </c>
       <c r="B175" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C175">
         <v>27</v>
@@ -5007,7 +5007,7 @@
         <v>26917</v>
       </c>
       <c r="B176" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C176">
         <v>27</v>
@@ -5033,7 +5033,7 @@
         <v>26918</v>
       </c>
       <c r="B177" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C177">
         <v>27</v>
@@ -5059,7 +5059,7 @@
         <v>26919</v>
       </c>
       <c r="B178" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C178">
         <v>28</v>
@@ -5085,7 +5085,7 @@
         <v>26920</v>
       </c>
       <c r="B179" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C179">
         <v>28</v>
@@ -5111,7 +5111,7 @@
         <v>26921</v>
       </c>
       <c r="B180" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C180">
         <v>28</v>
@@ -5137,7 +5137,7 @@
         <v>26922</v>
       </c>
       <c r="B181" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C181">
         <v>28</v>
@@ -5163,7 +5163,7 @@
         <v>26923</v>
       </c>
       <c r="B182" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C182">
         <v>28</v>
@@ -5189,7 +5189,7 @@
         <v>26924</v>
       </c>
       <c r="B183" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C183">
         <v>29</v>
@@ -5215,7 +5215,7 @@
         <v>26925</v>
       </c>
       <c r="B184" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C184">
         <v>29</v>
@@ -5241,7 +5241,7 @@
         <v>26926</v>
       </c>
       <c r="B185" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C185">
         <v>29</v>
@@ -5267,7 +5267,7 @@
         <v>26927</v>
       </c>
       <c r="B186" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C186">
         <v>29</v>
@@ -5293,7 +5293,7 @@
         <v>26928</v>
       </c>
       <c r="B187" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C187">
         <v>29</v>
@@ -5319,7 +5319,7 @@
         <v>26929</v>
       </c>
       <c r="B188" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C188">
         <v>30</v>
@@ -5345,7 +5345,7 @@
         <v>26930</v>
       </c>
       <c r="B189" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C189">
         <v>30</v>
@@ -5371,7 +5371,7 @@
         <v>26931</v>
       </c>
       <c r="B190" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C190">
         <v>30</v>
@@ -5397,7 +5397,7 @@
         <v>26932</v>
       </c>
       <c r="B191" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C191">
         <v>30</v>
@@ -5423,7 +5423,7 @@
         <v>26933</v>
       </c>
       <c r="B192" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C192">
         <v>30</v>
@@ -5449,7 +5449,7 @@
         <v>26934</v>
       </c>
       <c r="B193" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C193">
         <v>31</v>
@@ -5475,7 +5475,7 @@
         <v>26935</v>
       </c>
       <c r="B194" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C194">
         <v>31</v>
@@ -5501,7 +5501,7 @@
         <v>26936</v>
       </c>
       <c r="B195" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C195">
         <v>31</v>
@@ -5527,7 +5527,7 @@
         <v>26937</v>
       </c>
       <c r="B196" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C196">
         <v>31</v>
@@ -5553,7 +5553,7 @@
         <v>26938</v>
       </c>
       <c r="B197" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C197">
         <v>31</v>
@@ -5579,7 +5579,7 @@
         <v>26939</v>
       </c>
       <c r="B198" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C198">
         <v>31</v>
@@ -5605,7 +5605,7 @@
         <v>26940</v>
       </c>
       <c r="B199" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C199">
         <v>31</v>
@@ -5631,7 +5631,7 @@
         <v>26941</v>
       </c>
       <c r="B200" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -5657,7 +5657,7 @@
         <v>26942</v>
       </c>
       <c r="B201" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -5683,7 +5683,7 @@
         <v>26943</v>
       </c>
       <c r="B202" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -5709,7 +5709,7 @@
         <v>26944</v>
       </c>
       <c r="B203" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -5735,7 +5735,7 @@
         <v>26945</v>
       </c>
       <c r="B204" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C204">
         <v>2</v>
@@ -5761,7 +5761,7 @@
         <v>26946</v>
       </c>
       <c r="B205" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C205">
         <v>2</v>
@@ -5787,7 +5787,7 @@
         <v>26947</v>
       </c>
       <c r="B206" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C206">
         <v>2</v>
@@ -5813,7 +5813,7 @@
         <v>26948</v>
       </c>
       <c r="B207" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C207">
         <v>2</v>
@@ -5839,7 +5839,7 @@
         <v>26949</v>
       </c>
       <c r="B208" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C208">
         <v>2</v>
@@ -5865,7 +5865,7 @@
         <v>26950</v>
       </c>
       <c r="B209" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C209">
         <v>3</v>
@@ -5891,7 +5891,7 @@
         <v>26951</v>
       </c>
       <c r="B210" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C210">
         <v>3</v>
@@ -5917,7 +5917,7 @@
         <v>26952</v>
       </c>
       <c r="B211" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C211">
         <v>3</v>
@@ -5943,7 +5943,7 @@
         <v>26953</v>
       </c>
       <c r="B212" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C212">
         <v>3</v>
@@ -5969,7 +5969,7 @@
         <v>26954</v>
       </c>
       <c r="B213" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C213">
         <v>3</v>
@@ -5995,7 +5995,7 @@
         <v>26955</v>
       </c>
       <c r="B214" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -6021,7 +6021,7 @@
         <v>26956</v>
       </c>
       <c r="B215" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C215">
         <v>4</v>
@@ -6047,7 +6047,7 @@
         <v>26957</v>
       </c>
       <c r="B216" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C216">
         <v>4</v>
@@ -6073,7 +6073,7 @@
         <v>26958</v>
       </c>
       <c r="B217" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C217">
         <v>4</v>
@@ -6099,7 +6099,7 @@
         <v>26959</v>
       </c>
       <c r="B218" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C218">
         <v>4</v>
@@ -6125,7 +6125,7 @@
         <v>26960</v>
       </c>
       <c r="B219" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C219">
         <v>5</v>
@@ -6151,7 +6151,7 @@
         <v>26961</v>
       </c>
       <c r="B220" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C220">
         <v>5</v>
@@ -6177,7 +6177,7 @@
         <v>26962</v>
       </c>
       <c r="B221" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C221">
         <v>5</v>
@@ -6203,7 +6203,7 @@
         <v>26963</v>
       </c>
       <c r="B222" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C222">
         <v>5</v>
@@ -6229,7 +6229,7 @@
         <v>26964</v>
       </c>
       <c r="B223" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C223">
         <v>5</v>
@@ -6255,7 +6255,7 @@
         <v>26965</v>
       </c>
       <c r="B224" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C224">
         <v>5</v>
@@ -6281,7 +6281,7 @@
         <v>26966</v>
       </c>
       <c r="B225" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C225">
         <v>6</v>
@@ -6307,7 +6307,7 @@
         <v>26967</v>
       </c>
       <c r="B226" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C226">
         <v>6</v>
@@ -6333,7 +6333,7 @@
         <v>26968</v>
       </c>
       <c r="B227" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C227">
         <v>6</v>
@@ -6359,7 +6359,7 @@
         <v>26969</v>
       </c>
       <c r="B228" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C228">
         <v>6</v>
@@ -6385,7 +6385,7 @@
         <v>26970</v>
       </c>
       <c r="B229" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C229">
         <v>6</v>
@@ -6411,7 +6411,7 @@
         <v>26971</v>
       </c>
       <c r="B230" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C230">
         <v>7</v>
@@ -6437,7 +6437,7 @@
         <v>26972</v>
       </c>
       <c r="B231" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C231">
         <v>7</v>
@@ -6463,7 +6463,7 @@
         <v>26973</v>
       </c>
       <c r="B232" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C232">
         <v>7</v>
@@ -6489,7 +6489,7 @@
         <v>26974</v>
       </c>
       <c r="B233" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C233">
         <v>7</v>
@@ -6515,7 +6515,7 @@
         <v>26975</v>
       </c>
       <c r="B234" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C234">
         <v>8</v>
@@ -6541,7 +6541,7 @@
         <v>26976</v>
       </c>
       <c r="B235" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C235">
         <v>8</v>
@@ -6567,7 +6567,7 @@
         <v>26977</v>
       </c>
       <c r="B236" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C236">
         <v>8</v>
@@ -6593,7 +6593,7 @@
         <v>26978</v>
       </c>
       <c r="B237" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C237">
         <v>8</v>
@@ -6619,7 +6619,7 @@
         <v>26979</v>
       </c>
       <c r="B238" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C238">
         <v>8</v>
@@ -6645,7 +6645,7 @@
         <v>26980</v>
       </c>
       <c r="B239" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C239">
         <v>9</v>
@@ -6671,7 +6671,7 @@
         <v>26981</v>
       </c>
       <c r="B240" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C240">
         <v>9</v>
@@ -6697,7 +6697,7 @@
         <v>26982</v>
       </c>
       <c r="B241" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C241">
         <v>9</v>
@@ -6723,7 +6723,7 @@
         <v>26983</v>
       </c>
       <c r="B242" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C242">
         <v>9</v>
@@ -6749,7 +6749,7 @@
         <v>26984</v>
       </c>
       <c r="B243" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C243">
         <v>9</v>
@@ -6775,7 +6775,7 @@
         <v>26985</v>
       </c>
       <c r="B244" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C244">
         <v>9</v>
@@ -6801,7 +6801,7 @@
         <v>26986</v>
       </c>
       <c r="B245" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C245">
         <v>10</v>
@@ -6827,7 +6827,7 @@
         <v>26987</v>
       </c>
       <c r="B246" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C246">
         <v>10</v>
@@ -6853,7 +6853,7 @@
         <v>26988</v>
       </c>
       <c r="B247" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C247">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>26989</v>
       </c>
       <c r="B248" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C248">
         <v>10</v>
@@ -6905,7 +6905,7 @@
         <v>26990</v>
       </c>
       <c r="B249" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C249">
         <v>11</v>
@@ -6931,7 +6931,7 @@
         <v>26991</v>
       </c>
       <c r="B250" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C250">
         <v>11</v>
@@ -6957,7 +6957,7 @@
         <v>26992</v>
       </c>
       <c r="B251" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C251">
         <v>11</v>
@@ -6983,7 +6983,7 @@
         <v>26993</v>
       </c>
       <c r="B252" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C252">
         <v>11</v>
@@ -7009,7 +7009,7 @@
         <v>26994</v>
       </c>
       <c r="B253" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C253">
         <v>11</v>
@@ -7035,7 +7035,7 @@
         <v>26995</v>
       </c>
       <c r="B254" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C254">
         <v>12</v>
@@ -7061,7 +7061,7 @@
         <v>26996</v>
       </c>
       <c r="B255" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C255">
         <v>12</v>
@@ -7087,7 +7087,7 @@
         <v>26997</v>
       </c>
       <c r="B256" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C256">
         <v>12</v>
@@ -7113,7 +7113,7 @@
         <v>26998</v>
       </c>
       <c r="B257" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C257">
         <v>12</v>
@@ -7139,7 +7139,7 @@
         <v>26999</v>
       </c>
       <c r="B258" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C258">
         <v>13</v>
@@ -7165,7 +7165,7 @@
         <v>27000</v>
       </c>
       <c r="B259" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C259">
         <v>13</v>
@@ -7191,7 +7191,7 @@
         <v>27001</v>
       </c>
       <c r="B260" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C260">
         <v>13</v>
@@ -7217,7 +7217,7 @@
         <v>27002</v>
       </c>
       <c r="B261" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C261">
         <v>13</v>
@@ -7243,7 +7243,7 @@
         <v>27003</v>
       </c>
       <c r="B262" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C262">
         <v>13</v>
@@ -7269,7 +7269,7 @@
         <v>27004</v>
       </c>
       <c r="B263" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C263">
         <v>13</v>
@@ -7292,7 +7292,7 @@
         <v>27005</v>
       </c>
       <c r="B264" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C264">
         <v>14</v>
@@ -7318,7 +7318,7 @@
         <v>27006</v>
       </c>
       <c r="B265" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C265">
         <v>14</v>
@@ -7344,7 +7344,7 @@
         <v>27007</v>
       </c>
       <c r="B266" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C266">
         <v>14</v>
@@ -7370,7 +7370,7 @@
         <v>27008</v>
       </c>
       <c r="B267" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C267">
         <v>14</v>
@@ -7396,7 +7396,7 @@
         <v>27009</v>
       </c>
       <c r="B268" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C268">
         <v>15</v>
@@ -7422,7 +7422,7 @@
         <v>27010</v>
       </c>
       <c r="B269" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C269">
         <v>15</v>
@@ -7448,7 +7448,7 @@
         <v>27011</v>
       </c>
       <c r="B270" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C270">
         <v>15</v>
@@ -7474,7 +7474,7 @@
         <v>27012</v>
       </c>
       <c r="B271" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C271">
         <v>15</v>
@@ -7500,7 +7500,7 @@
         <v>27013</v>
       </c>
       <c r="B272" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C272">
         <v>15</v>
@@ -7526,7 +7526,7 @@
         <v>27014</v>
       </c>
       <c r="B273" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C273">
         <v>15</v>
@@ -7552,7 +7552,7 @@
         <v>27015</v>
       </c>
       <c r="B274" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C274">
         <v>16</v>
@@ -7578,7 +7578,7 @@
         <v>27016</v>
       </c>
       <c r="B275" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C275">
         <v>16</v>
@@ -7604,7 +7604,7 @@
         <v>27017</v>
       </c>
       <c r="B276" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C276">
         <v>16</v>
@@ -7630,7 +7630,7 @@
         <v>27018</v>
       </c>
       <c r="B277" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C277">
         <v>16</v>
@@ -7656,7 +7656,7 @@
         <v>27019</v>
       </c>
       <c r="B278" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C278">
         <v>17</v>
@@ -7682,7 +7682,7 @@
         <v>27020</v>
       </c>
       <c r="B279" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C279">
         <v>17</v>
@@ -7708,7 +7708,7 @@
         <v>27021</v>
       </c>
       <c r="B280" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C280">
         <v>17</v>
@@ -7734,7 +7734,7 @@
         <v>27022</v>
       </c>
       <c r="B281" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C281">
         <v>17</v>
@@ -7760,7 +7760,7 @@
         <v>27023</v>
       </c>
       <c r="B282" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C282">
         <v>17</v>
@@ -7786,7 +7786,7 @@
         <v>27024</v>
       </c>
       <c r="B283" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C283">
         <v>17</v>
@@ -7812,7 +7812,7 @@
         <v>27025</v>
       </c>
       <c r="B284" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C284">
         <v>17</v>
@@ -7838,7 +7838,7 @@
         <v>27026</v>
       </c>
       <c r="B285" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C285">
         <v>18</v>
@@ -7864,7 +7864,7 @@
         <v>27027</v>
       </c>
       <c r="B286" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C286">
         <v>18</v>
@@ -7890,7 +7890,7 @@
         <v>27028</v>
       </c>
       <c r="B287" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C287">
         <v>18</v>
@@ -7916,7 +7916,7 @@
         <v>27029</v>
       </c>
       <c r="B288" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C288">
         <v>19</v>
@@ -7942,7 +7942,7 @@
         <v>27030</v>
       </c>
       <c r="B289" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C289">
         <v>19</v>
@@ -7968,7 +7968,7 @@
         <v>27031</v>
       </c>
       <c r="B290" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C290">
         <v>19</v>
@@ -7994,7 +7994,7 @@
         <v>27032</v>
       </c>
       <c r="B291" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C291">
         <v>19</v>
@@ -8020,7 +8020,7 @@
         <v>27033</v>
       </c>
       <c r="B292" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C292">
         <v>19</v>
@@ -8046,7 +8046,7 @@
         <v>27034</v>
       </c>
       <c r="B293" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C293">
         <v>19</v>
@@ -8072,7 +8072,7 @@
         <v>27035</v>
       </c>
       <c r="B294" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C294">
         <v>20</v>
@@ -8098,7 +8098,7 @@
         <v>27036</v>
       </c>
       <c r="B295" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C295">
         <v>20</v>
@@ -8124,7 +8124,7 @@
         <v>27037</v>
       </c>
       <c r="B296" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C296">
         <v>20</v>
@@ -8150,7 +8150,7 @@
         <v>27038</v>
       </c>
       <c r="B297" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C297">
         <v>20</v>
@@ -8176,7 +8176,7 @@
         <v>27039</v>
       </c>
       <c r="B298" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C298">
         <v>20</v>
@@ -8202,7 +8202,7 @@
         <v>27040</v>
       </c>
       <c r="B299" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C299">
         <v>21</v>
@@ -8228,7 +8228,7 @@
         <v>27041</v>
       </c>
       <c r="B300" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C300">
         <v>21</v>
@@ -8254,7 +8254,7 @@
         <v>27042</v>
       </c>
       <c r="B301" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C301">
         <v>21</v>
@@ -8280,7 +8280,7 @@
         <v>27043</v>
       </c>
       <c r="B302" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C302">
         <v>21</v>
@@ -8306,7 +8306,7 @@
         <v>27044</v>
       </c>
       <c r="B303" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C303">
         <v>21</v>
@@ -8332,7 +8332,7 @@
         <v>27045</v>
       </c>
       <c r="B304" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C304">
         <v>22</v>
@@ -8358,7 +8358,7 @@
         <v>27046</v>
       </c>
       <c r="B305" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C305">
         <v>22</v>
@@ -8384,7 +8384,7 @@
         <v>27047</v>
       </c>
       <c r="B306" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C306">
         <v>22</v>
@@ -8410,7 +8410,7 @@
         <v>27048</v>
       </c>
       <c r="B307" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C307">
         <v>22</v>
@@ -8436,7 +8436,7 @@
         <v>27049</v>
       </c>
       <c r="B308" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C308">
         <v>22</v>
@@ -8462,7 +8462,7 @@
         <v>27050</v>
       </c>
       <c r="B309" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C309">
         <v>23</v>
@@ -8488,7 +8488,7 @@
         <v>27051</v>
       </c>
       <c r="B310" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C310">
         <v>23</v>
@@ -8514,7 +8514,7 @@
         <v>27052</v>
       </c>
       <c r="B311" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C311">
         <v>23</v>
@@ -8540,7 +8540,7 @@
         <v>27053</v>
       </c>
       <c r="B312" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C312">
         <v>23</v>
@@ -8566,7 +8566,7 @@
         <v>27054</v>
       </c>
       <c r="B313" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C313">
         <v>23</v>
@@ -8592,7 +8592,7 @@
         <v>27055</v>
       </c>
       <c r="B314" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C314">
         <v>24</v>
@@ -8618,7 +8618,7 @@
         <v>27056</v>
       </c>
       <c r="B315" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C315">
         <v>24</v>
@@ -8644,7 +8644,7 @@
         <v>27057</v>
       </c>
       <c r="B316" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C316">
         <v>24</v>
@@ -8670,7 +8670,7 @@
         <v>27058</v>
       </c>
       <c r="B317" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C317">
         <v>24</v>
@@ -8693,7 +8693,7 @@
         <v>27059</v>
       </c>
       <c r="B318" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -8716,7 +8716,7 @@
         <v>27060</v>
       </c>
       <c r="B319" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C319">
         <v>25</v>
@@ -8742,7 +8742,7 @@
         <v>27061</v>
       </c>
       <c r="B320" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C320">
         <v>25</v>
@@ -8768,7 +8768,7 @@
         <v>27062</v>
       </c>
       <c r="B321" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C321">
         <v>25</v>
@@ -8794,7 +8794,7 @@
         <v>27063</v>
       </c>
       <c r="B322" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C322">
         <v>25</v>
@@ -8820,7 +8820,7 @@
         <v>27064</v>
       </c>
       <c r="B323" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C323">
         <v>25</v>
@@ -8846,7 +8846,7 @@
         <v>27065</v>
       </c>
       <c r="B324" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C324">
         <v>26</v>
@@ -8872,7 +8872,7 @@
         <v>27066</v>
       </c>
       <c r="B325" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C325">
         <v>26</v>
@@ -8898,7 +8898,7 @@
         <v>27067</v>
       </c>
       <c r="B326" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C326">
         <v>26</v>
@@ -8924,7 +8924,7 @@
         <v>27068</v>
       </c>
       <c r="B327" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C327">
         <v>26</v>
@@ -8950,7 +8950,7 @@
         <v>27069</v>
       </c>
       <c r="B328" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C328">
         <v>26</v>
@@ -8976,7 +8976,7 @@
         <v>27070</v>
       </c>
       <c r="B329" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C329">
         <v>26</v>
@@ -9002,7 +9002,7 @@
         <v>27071</v>
       </c>
       <c r="B330" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C330">
         <v>27</v>
@@ -9028,7 +9028,7 @@
         <v>27072</v>
       </c>
       <c r="B331" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C331">
         <v>27</v>
@@ -9054,7 +9054,7 @@
         <v>27073</v>
       </c>
       <c r="B332" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C332">
         <v>27</v>
@@ -9080,7 +9080,7 @@
         <v>27074</v>
       </c>
       <c r="B333" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C333">
         <v>27</v>
@@ -9106,7 +9106,7 @@
         <v>27075</v>
       </c>
       <c r="B334" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C334">
         <v>28</v>
@@ -9132,7 +9132,7 @@
         <v>27076</v>
       </c>
       <c r="B335" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C335">
         <v>28</v>
@@ -9158,7 +9158,7 @@
         <v>27077</v>
       </c>
       <c r="B336" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C336">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27078</v>
       </c>
       <c r="B337" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C337">
         <v>28</v>
@@ -9210,7 +9210,7 @@
         <v>27079</v>
       </c>
       <c r="B338" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C338">
         <v>28</v>
@@ -9236,7 +9236,7 @@
         <v>27080</v>
       </c>
       <c r="B339" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C339">
         <v>28</v>
@@ -9262,7 +9262,7 @@
         <v>27081</v>
       </c>
       <c r="B340" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9288,7 +9288,7 @@
         <v>27082</v>
       </c>
       <c r="B341" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9314,7 +9314,7 @@
         <v>27083</v>
       </c>
       <c r="B342" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9340,7 +9340,7 @@
         <v>27084</v>
       </c>
       <c r="B343" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9366,7 +9366,7 @@
         <v>27085</v>
       </c>
       <c r="B344" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9392,7 +9392,7 @@
         <v>27086</v>
       </c>
       <c r="B345" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C345">
         <v>2</v>
@@ -9418,7 +9418,7 @@
         <v>27087</v>
       </c>
       <c r="B346" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C346">
         <v>2</v>
@@ -9444,7 +9444,7 @@
         <v>27088</v>
       </c>
       <c r="B347" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C347">
         <v>2</v>
@@ -9470,7 +9470,7 @@
         <v>27089</v>
       </c>
       <c r="B348" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C348">
         <v>2</v>
@@ -9496,7 +9496,7 @@
         <v>27090</v>
       </c>
       <c r="B349" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C349">
         <v>2</v>
@@ -9522,7 +9522,7 @@
         <v>27091</v>
       </c>
       <c r="B350" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C350">
         <v>3</v>
@@ -9548,7 +9548,7 @@
         <v>27092</v>
       </c>
       <c r="B351" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C351">
         <v>3</v>
@@ -9574,7 +9574,7 @@
         <v>27093</v>
       </c>
       <c r="B352" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C352">
         <v>3</v>
@@ -9600,7 +9600,7 @@
         <v>27094</v>
       </c>
       <c r="B353" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C353">
         <v>3</v>
@@ -9626,7 +9626,7 @@
         <v>27095</v>
       </c>
       <c r="B354" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C354">
         <v>3</v>
@@ -9652,7 +9652,7 @@
         <v>27096</v>
       </c>
       <c r="B355" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C355">
         <v>4</v>
@@ -9678,7 +9678,7 @@
         <v>27097</v>
       </c>
       <c r="B356" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C356">
         <v>4</v>
@@ -9704,7 +9704,7 @@
         <v>27098</v>
       </c>
       <c r="B357" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C357">
         <v>4</v>
@@ -9730,7 +9730,7 @@
         <v>27099</v>
       </c>
       <c r="B358" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C358">
         <v>4</v>
@@ -9756,7 +9756,7 @@
         <v>27100</v>
       </c>
       <c r="B359" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C359">
         <v>4</v>
@@ -9782,7 +9782,7 @@
         <v>27101</v>
       </c>
       <c r="B360" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C360">
         <v>5</v>
@@ -9808,7 +9808,7 @@
         <v>27102</v>
       </c>
       <c r="B361" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C361">
         <v>5</v>
@@ -9834,7 +9834,7 @@
         <v>27103</v>
       </c>
       <c r="B362" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C362">
         <v>5</v>
@@ -9860,7 +9860,7 @@
         <v>27104</v>
       </c>
       <c r="B363" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C363">
         <v>5</v>
@@ -9886,7 +9886,7 @@
         <v>27105</v>
       </c>
       <c r="B364" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C364">
         <v>5</v>
@@ -9912,7 +9912,7 @@
         <v>27106</v>
       </c>
       <c r="B365" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C365">
         <v>6</v>
@@ -9938,7 +9938,7 @@
         <v>27107</v>
       </c>
       <c r="B366" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C366">
         <v>6</v>
@@ -9964,7 +9964,7 @@
         <v>27108</v>
       </c>
       <c r="B367" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C367">
         <v>6</v>
@@ -9990,7 +9990,7 @@
         <v>27109</v>
       </c>
       <c r="B368" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C368">
         <v>6</v>
@@ -10016,7 +10016,7 @@
         <v>27110</v>
       </c>
       <c r="B369" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C369">
         <v>6</v>
@@ -10042,7 +10042,7 @@
         <v>27111</v>
       </c>
       <c r="B370" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C370">
         <v>6</v>
@@ -10068,7 +10068,7 @@
         <v>27112</v>
       </c>
       <c r="B371" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C371">
         <v>7</v>
@@ -10094,7 +10094,7 @@
         <v>27113</v>
       </c>
       <c r="B372" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C372">
         <v>7</v>
@@ -10120,7 +10120,7 @@
         <v>27114</v>
       </c>
       <c r="B373" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C373">
         <v>7</v>
@@ -10146,7 +10146,7 @@
         <v>27115</v>
       </c>
       <c r="B374" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C374">
         <v>7</v>
@@ -10172,7 +10172,7 @@
         <v>27116</v>
       </c>
       <c r="B375" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C375">
         <v>7</v>
@@ -10198,7 +10198,7 @@
         <v>27117</v>
       </c>
       <c r="B376" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C376">
         <v>8</v>
@@ -10224,7 +10224,7 @@
         <v>27118</v>
       </c>
       <c r="B377" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C377">
         <v>8</v>
@@ -10250,7 +10250,7 @@
         <v>27119</v>
       </c>
       <c r="B378" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C378">
         <v>8</v>
@@ -10276,7 +10276,7 @@
         <v>27120</v>
       </c>
       <c r="B379" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C379">
         <v>8</v>
@@ -10302,7 +10302,7 @@
         <v>27121</v>
       </c>
       <c r="B380" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C380">
         <v>8</v>
@@ -10328,7 +10328,7 @@
         <v>27122</v>
       </c>
       <c r="B381" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C381">
         <v>9</v>
@@ -10354,7 +10354,7 @@
         <v>27123</v>
       </c>
       <c r="B382" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C382">
         <v>9</v>
@@ -10380,7 +10380,7 @@
         <v>27124</v>
       </c>
       <c r="B383" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C383">
         <v>9</v>
@@ -10406,7 +10406,7 @@
         <v>27125</v>
       </c>
       <c r="B384" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C384">
         <v>9</v>
@@ -10432,7 +10432,7 @@
         <v>27126</v>
       </c>
       <c r="B385" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C385">
         <v>10</v>
@@ -10458,7 +10458,7 @@
         <v>27127</v>
       </c>
       <c r="B386" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C386">
         <v>10</v>
@@ -10484,7 +10484,7 @@
         <v>27128</v>
       </c>
       <c r="B387" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C387">
         <v>10</v>
@@ -10510,7 +10510,7 @@
         <v>27129</v>
       </c>
       <c r="B388" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C388">
         <v>10</v>
@@ -10536,7 +10536,7 @@
         <v>27130</v>
       </c>
       <c r="B389" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C389">
         <v>10</v>
@@ -10562,7 +10562,7 @@
         <v>27131</v>
       </c>
       <c r="B390" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C390">
         <v>11</v>
@@ -10588,7 +10588,7 @@
         <v>27132</v>
       </c>
       <c r="B391" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C391">
         <v>11</v>
@@ -10614,7 +10614,7 @@
         <v>27133</v>
       </c>
       <c r="B392" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C392">
         <v>11</v>
@@ -10640,7 +10640,7 @@
         <v>27134</v>
       </c>
       <c r="B393" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C393">
         <v>11</v>
@@ -10666,7 +10666,7 @@
         <v>27135</v>
       </c>
       <c r="B394" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C394">
         <v>11</v>
@@ -10692,7 +10692,7 @@
         <v>27136</v>
       </c>
       <c r="B395" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C395">
         <v>12</v>
@@ -10718,7 +10718,7 @@
         <v>27137</v>
       </c>
       <c r="B396" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C396">
         <v>12</v>
@@ -10744,7 +10744,7 @@
         <v>27138</v>
       </c>
       <c r="B397" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C397">
         <v>12</v>
@@ -10770,7 +10770,7 @@
         <v>27139</v>
       </c>
       <c r="B398" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C398">
         <v>12</v>
@@ -10796,7 +10796,7 @@
         <v>27140</v>
       </c>
       <c r="B399" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C399">
         <v>12</v>
@@ -10822,7 +10822,7 @@
         <v>27141</v>
       </c>
       <c r="B400" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C400">
         <v>12</v>
@@ -10848,7 +10848,7 @@
         <v>27142</v>
       </c>
       <c r="B401" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C401">
         <v>13</v>
@@ -10874,7 +10874,7 @@
         <v>27143</v>
       </c>
       <c r="B402" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C402">
         <v>13</v>
@@ -10900,7 +10900,7 @@
         <v>27144</v>
       </c>
       <c r="B403" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C403">
         <v>13</v>
@@ -10926,7 +10926,7 @@
         <v>27145</v>
       </c>
       <c r="B404" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C404">
         <v>13</v>
@@ -10952,7 +10952,7 @@
         <v>27146</v>
       </c>
       <c r="B405" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C405">
         <v>14</v>
@@ -10978,7 +10978,7 @@
         <v>27147</v>
       </c>
       <c r="B406" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C406">
         <v>14</v>
@@ -11004,7 +11004,7 @@
         <v>27148</v>
       </c>
       <c r="B407" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C407">
         <v>14</v>
@@ -11030,7 +11030,7 @@
         <v>27149</v>
       </c>
       <c r="B408" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C408">
         <v>14</v>
@@ -11056,7 +11056,7 @@
         <v>27150</v>
       </c>
       <c r="B409" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C409">
         <v>14</v>
@@ -11082,7 +11082,7 @@
         <v>27151</v>
       </c>
       <c r="B410" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C410">
         <v>15</v>
@@ -11108,7 +11108,7 @@
         <v>27152</v>
       </c>
       <c r="B411" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C411">
         <v>15</v>
@@ -11134,7 +11134,7 @@
         <v>27153</v>
       </c>
       <c r="B412" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C412">
         <v>15</v>
@@ -11160,7 +11160,7 @@
         <v>27154</v>
       </c>
       <c r="B413" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C413">
         <v>15</v>
@@ -11186,7 +11186,7 @@
         <v>27155</v>
       </c>
       <c r="B414" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C414">
         <v>15</v>
@@ -11212,7 +11212,7 @@
         <v>27156</v>
       </c>
       <c r="B415" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C415">
         <v>15</v>
@@ -11238,7 +11238,7 @@
         <v>27157</v>
       </c>
       <c r="B416" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C416">
         <v>16</v>
@@ -11264,7 +11264,7 @@
         <v>27158</v>
       </c>
       <c r="B417" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C417">
         <v>16</v>
@@ -11290,7 +11290,7 @@
         <v>27159</v>
       </c>
       <c r="B418" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C418">
         <v>16</v>
@@ -11316,7 +11316,7 @@
         <v>27160</v>
       </c>
       <c r="B419" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C419">
         <v>16</v>
@@ -11342,7 +11342,7 @@
         <v>27161</v>
       </c>
       <c r="B420" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C420">
         <v>17</v>
@@ -11368,7 +11368,7 @@
         <v>27162</v>
       </c>
       <c r="B421" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C421">
         <v>17</v>
@@ -11394,7 +11394,7 @@
         <v>27163</v>
       </c>
       <c r="B422" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C422">
         <v>17</v>
@@ -11420,7 +11420,7 @@
         <v>27164</v>
       </c>
       <c r="B423" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C423">
         <v>17</v>
@@ -11446,7 +11446,7 @@
         <v>27165</v>
       </c>
       <c r="B424" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C424">
         <v>17</v>
@@ -11472,7 +11472,7 @@
         <v>27166</v>
       </c>
       <c r="B425" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C425">
         <v>18</v>
@@ -11498,7 +11498,7 @@
         <v>27167</v>
       </c>
       <c r="B426" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C426">
         <v>18</v>
@@ -11524,7 +11524,7 @@
         <v>27168</v>
       </c>
       <c r="B427" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C427">
         <v>18</v>
@@ -11550,7 +11550,7 @@
         <v>27169</v>
       </c>
       <c r="B428" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C428">
         <v>18</v>
@@ -11576,7 +11576,7 @@
         <v>27170</v>
       </c>
       <c r="B429" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C429">
         <v>19</v>
@@ -11602,7 +11602,7 @@
         <v>27171</v>
       </c>
       <c r="B430" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C430">
         <v>19</v>
@@ -11628,7 +11628,7 @@
         <v>27172</v>
       </c>
       <c r="B431" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C431">
         <v>19</v>
@@ -11651,7 +11651,7 @@
         <v>27173</v>
       </c>
       <c r="B432" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C432">
         <v>19</v>
@@ -11677,7 +11677,7 @@
         <v>27174</v>
       </c>
       <c r="B433" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C433">
         <v>19</v>
@@ -11703,7 +11703,7 @@
         <v>27175</v>
       </c>
       <c r="B434" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C434">
         <v>19</v>
@@ -11729,7 +11729,7 @@
         <v>27176</v>
       </c>
       <c r="B435" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C435">
         <v>20</v>
@@ -11755,7 +11755,7 @@
         <v>27177</v>
       </c>
       <c r="B436" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C436">
         <v>20</v>
@@ -11781,7 +11781,7 @@
         <v>27178</v>
       </c>
       <c r="B437" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C437">
         <v>20</v>
@@ -11807,7 +11807,7 @@
         <v>27179</v>
       </c>
       <c r="B438" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C438">
         <v>20</v>
@@ -11833,7 +11833,7 @@
         <v>27180</v>
       </c>
       <c r="B439" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C439">
         <v>21</v>
@@ -11859,7 +11859,7 @@
         <v>27181</v>
       </c>
       <c r="B440" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C440">
         <v>21</v>
@@ -11885,7 +11885,7 @@
         <v>27182</v>
       </c>
       <c r="B441" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C441">
         <v>21</v>
@@ -11911,7 +11911,7 @@
         <v>27183</v>
       </c>
       <c r="B442" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C442">
         <v>21</v>
@@ -11937,7 +11937,7 @@
         <v>27184</v>
       </c>
       <c r="B443" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C443">
         <v>21</v>
@@ -11963,7 +11963,7 @@
         <v>27185</v>
       </c>
       <c r="B444" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C444">
         <v>21</v>
@@ -11989,7 +11989,7 @@
         <v>27186</v>
       </c>
       <c r="B445" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C445">
         <v>22</v>
@@ -12012,7 +12012,7 @@
         <v>27187</v>
       </c>
       <c r="B446" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C446">
         <v>22</v>
@@ -12038,7 +12038,7 @@
         <v>27188</v>
       </c>
       <c r="B447" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C447">
         <v>22</v>
@@ -12064,7 +12064,7 @@
         <v>27189</v>
       </c>
       <c r="B448" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C448">
         <v>22</v>
@@ -12090,7 +12090,7 @@
         <v>27190</v>
       </c>
       <c r="B449" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C449">
         <v>22</v>
@@ -12116,7 +12116,7 @@
         <v>27191</v>
       </c>
       <c r="B450" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C450">
         <v>23</v>
@@ -12142,7 +12142,7 @@
         <v>27192</v>
       </c>
       <c r="B451" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C451">
         <v>23</v>
@@ -12168,7 +12168,7 @@
         <v>27193</v>
       </c>
       <c r="B452" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C452">
         <v>23</v>
@@ -12194,7 +12194,7 @@
         <v>27194</v>
       </c>
       <c r="B453" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C453">
         <v>23</v>
@@ -12220,7 +12220,7 @@
         <v>27195</v>
       </c>
       <c r="B454" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C454">
         <v>23</v>
@@ -12246,7 +12246,7 @@
         <v>27196</v>
       </c>
       <c r="B455" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C455">
         <v>23</v>
@@ -12272,7 +12272,7 @@
         <v>27197</v>
       </c>
       <c r="B456" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C456">
         <v>24</v>
@@ -12298,7 +12298,7 @@
         <v>27198</v>
       </c>
       <c r="B457" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C457">
         <v>24</v>
@@ -12324,7 +12324,7 @@
         <v>27199</v>
       </c>
       <c r="B458" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C458">
         <v>24</v>
@@ -12350,7 +12350,7 @@
         <v>27200</v>
       </c>
       <c r="B459" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C459">
         <v>24</v>
@@ -12376,7 +12376,7 @@
         <v>27201</v>
       </c>
       <c r="B460" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C460">
         <v>24</v>
@@ -12402,7 +12402,7 @@
         <v>27202</v>
       </c>
       <c r="B461" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C461">
         <v>25</v>
@@ -12428,7 +12428,7 @@
         <v>27203</v>
       </c>
       <c r="B462" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C462">
         <v>25</v>
@@ -12454,7 +12454,7 @@
         <v>27204</v>
       </c>
       <c r="B463" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C463">
         <v>26</v>
@@ -12477,7 +12477,7 @@
         <v>27205</v>
       </c>
       <c r="B464" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C464">
         <v>26</v>
@@ -12503,7 +12503,7 @@
         <v>27206</v>
       </c>
       <c r="B465" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C465">
         <v>26</v>
@@ -12529,7 +12529,7 @@
         <v>27207</v>
       </c>
       <c r="B466" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C466">
         <v>26</v>
@@ -12555,7 +12555,7 @@
         <v>27208</v>
       </c>
       <c r="B467" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C467">
         <v>26</v>
@@ -12581,7 +12581,7 @@
         <v>27209</v>
       </c>
       <c r="B468" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C468">
         <v>26</v>
@@ -12607,7 +12607,7 @@
         <v>27210</v>
       </c>
       <c r="B469" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C469">
         <v>27</v>
@@ -12633,7 +12633,7 @@
         <v>27211</v>
       </c>
       <c r="B470" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C470">
         <v>27</v>
@@ -12659,7 +12659,7 @@
         <v>27212</v>
       </c>
       <c r="B471" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C471">
         <v>27</v>
@@ -12685,7 +12685,7 @@
         <v>27213</v>
       </c>
       <c r="B472" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C472">
         <v>27</v>
@@ -12711,7 +12711,7 @@
         <v>27214</v>
       </c>
       <c r="B473" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C473">
         <v>27</v>
@@ -12737,7 +12737,7 @@
         <v>27215</v>
       </c>
       <c r="B474" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C474">
         <v>27</v>
@@ -12763,7 +12763,7 @@
         <v>27216</v>
       </c>
       <c r="B475" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C475">
         <v>28</v>
@@ -12789,7 +12789,7 @@
         <v>27217</v>
       </c>
       <c r="B476" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C476">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27218</v>
       </c>
       <c r="B477" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C477">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27219</v>
       </c>
       <c r="B478" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C478">
         <v>28</v>
@@ -12867,7 +12867,7 @@
         <v>27220</v>
       </c>
       <c r="B479" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C479">
         <v>29</v>
@@ -12893,7 +12893,7 @@
         <v>27221</v>
       </c>
       <c r="B480" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C480">
         <v>29</v>
@@ -12919,7 +12919,7 @@
         <v>27222</v>
       </c>
       <c r="B481" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C481">
         <v>29</v>
@@ -12945,7 +12945,7 @@
         <v>27223</v>
       </c>
       <c r="B482" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C482">
         <v>29</v>
@@ -12971,7 +12971,7 @@
         <v>27224</v>
       </c>
       <c r="B483" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C483">
         <v>29</v>
@@ -12997,7 +12997,7 @@
         <v>27225</v>
       </c>
       <c r="B484" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C484">
         <v>30</v>
@@ -13023,7 +13023,7 @@
         <v>27226</v>
       </c>
       <c r="B485" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C485">
         <v>30</v>
@@ -13049,7 +13049,7 @@
         <v>27227</v>
       </c>
       <c r="B486" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C486">
         <v>30</v>
@@ -13072,7 +13072,7 @@
         <v>27228</v>
       </c>
       <c r="B487" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C487">
         <v>30</v>
@@ -13098,7 +13098,7 @@
         <v>27229</v>
       </c>
       <c r="B488" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C488">
         <v>30</v>
@@ -13124,7 +13124,7 @@
         <v>27230</v>
       </c>
       <c r="B489" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C489">
         <v>30</v>
@@ -13150,7 +13150,7 @@
         <v>27231</v>
       </c>
       <c r="B490" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C490">
         <v>31</v>
@@ -13176,7 +13176,7 @@
         <v>27232</v>
       </c>
       <c r="B491" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C491">
         <v>31</v>
@@ -13202,7 +13202,7 @@
         <v>27233</v>
       </c>
       <c r="B492" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C492">
         <v>31</v>
@@ -13228,7 +13228,7 @@
         <v>27234</v>
       </c>
       <c r="B493" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C493">
         <v>31</v>
@@ -13254,7 +13254,7 @@
         <v>27235</v>
       </c>
       <c r="B494" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C494">
         <v>31</v>
@@ -13280,7 +13280,7 @@
         <v>27236</v>
       </c>
       <c r="B495" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C495">
         <v>1</v>
@@ -13306,7 +13306,7 @@
         <v>27237</v>
       </c>
       <c r="B496" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C496">
         <v>1</v>
@@ -13332,7 +13332,7 @@
         <v>27238</v>
       </c>
       <c r="B497" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C497">
         <v>1</v>
@@ -13358,7 +13358,7 @@
         <v>27239</v>
       </c>
       <c r="B498" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C498">
         <v>1</v>
@@ -13384,7 +13384,7 @@
         <v>27240</v>
       </c>
       <c r="B499" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C499">
         <v>2</v>
@@ -13410,7 +13410,7 @@
         <v>27241</v>
       </c>
       <c r="B500" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C500">
         <v>2</v>
@@ -13436,7 +13436,7 @@
         <v>27242</v>
       </c>
       <c r="B501" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C501">
         <v>2</v>
@@ -13462,7 +13462,7 @@
         <v>27243</v>
       </c>
       <c r="B502" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C502">
         <v>2</v>
@@ -13488,7 +13488,7 @@
         <v>27244</v>
       </c>
       <c r="B503" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C503">
         <v>2</v>
@@ -13514,7 +13514,7 @@
         <v>27245</v>
       </c>
       <c r="B504" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C504">
         <v>2</v>
@@ -13540,7 +13540,7 @@
         <v>27246</v>
       </c>
       <c r="B505" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C505">
         <v>3</v>
@@ -13566,7 +13566,7 @@
         <v>27247</v>
       </c>
       <c r="B506" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C506">
         <v>3</v>
@@ -13592,7 +13592,7 @@
         <v>27248</v>
       </c>
       <c r="B507" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C507">
         <v>3</v>
@@ -13618,7 +13618,7 @@
         <v>27249</v>
       </c>
       <c r="B508" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C508">
         <v>3</v>
@@ -13644,7 +13644,7 @@
         <v>27250</v>
       </c>
       <c r="B509" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C509">
         <v>3</v>
@@ -13670,7 +13670,7 @@
         <v>27251</v>
       </c>
       <c r="B510" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C510">
         <v>4</v>
@@ -13696,7 +13696,7 @@
         <v>27252</v>
       </c>
       <c r="B511" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C511">
         <v>4</v>
@@ -13722,7 +13722,7 @@
         <v>27253</v>
       </c>
       <c r="B512" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C512">
         <v>4</v>
@@ -13748,7 +13748,7 @@
         <v>27254</v>
       </c>
       <c r="B513" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C513">
         <v>4</v>
@@ -13774,7 +13774,7 @@
         <v>27255</v>
       </c>
       <c r="B514" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C514">
         <v>4</v>
@@ -13800,7 +13800,7 @@
         <v>27256</v>
       </c>
       <c r="B515" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C515">
         <v>4</v>
@@ -13826,7 +13826,7 @@
         <v>27257</v>
       </c>
       <c r="B516" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C516">
         <v>5</v>
@@ -13852,7 +13852,7 @@
         <v>27258</v>
       </c>
       <c r="B517" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C517">
         <v>5</v>
@@ -13878,7 +13878,7 @@
         <v>27259</v>
       </c>
       <c r="B518" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C518">
         <v>5</v>
@@ -13904,7 +13904,7 @@
         <v>27260</v>
       </c>
       <c r="B519" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C519">
         <v>5</v>
@@ -13930,7 +13930,7 @@
         <v>27261</v>
       </c>
       <c r="B520" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C520">
         <v>5</v>
@@ -13956,7 +13956,7 @@
         <v>27262</v>
       </c>
       <c r="B521" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C521">
         <v>6</v>
@@ -13982,7 +13982,7 @@
         <v>27263</v>
       </c>
       <c r="B522" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C522">
         <v>6</v>
@@ -14008,7 +14008,7 @@
         <v>27264</v>
       </c>
       <c r="B523" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C523">
         <v>6</v>
@@ -14034,7 +14034,7 @@
         <v>27265</v>
       </c>
       <c r="B524" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C524">
         <v>6</v>
@@ -14060,7 +14060,7 @@
         <v>27266</v>
       </c>
       <c r="B525" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C525">
         <v>6</v>
@@ -14086,7 +14086,7 @@
         <v>27267</v>
       </c>
       <c r="B526" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C526">
         <v>7</v>
@@ -14112,7 +14112,7 @@
         <v>27267</v>
       </c>
       <c r="B527" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C527">
         <v>7</v>
@@ -14138,7 +14138,7 @@
         <v>27268</v>
       </c>
       <c r="B528" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C528">
         <v>7</v>
@@ -14164,7 +14164,7 @@
         <v>27269</v>
       </c>
       <c r="B529" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C529">
         <v>7</v>
@@ -14190,7 +14190,7 @@
         <v>27270</v>
       </c>
       <c r="B530" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C530">
         <v>7</v>
@@ -14216,7 +14216,7 @@
         <v>27271</v>
       </c>
       <c r="B531" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C531">
         <v>7</v>
@@ -14242,7 +14242,7 @@
         <v>27272</v>
       </c>
       <c r="B532" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C532">
         <v>8</v>
@@ -14268,7 +14268,7 @@
         <v>27273</v>
       </c>
       <c r="B533" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C533">
         <v>8</v>
@@ -14294,7 +14294,7 @@
         <v>27274</v>
       </c>
       <c r="B534" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C534">
         <v>8</v>
@@ -14320,7 +14320,7 @@
         <v>27275</v>
       </c>
       <c r="B535" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C535">
         <v>8</v>
@@ -14346,7 +14346,7 @@
         <v>27276</v>
       </c>
       <c r="B536" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C536">
         <v>9</v>
@@ -14372,7 +14372,7 @@
         <v>27277</v>
       </c>
       <c r="B537" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C537">
         <v>9</v>
@@ -14398,7 +14398,7 @@
         <v>27278</v>
       </c>
       <c r="B538" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C538">
         <v>9</v>
@@ -14424,7 +14424,7 @@
         <v>27279</v>
       </c>
       <c r="B539" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C539">
         <v>9</v>
@@ -14450,7 +14450,7 @@
         <v>27280</v>
       </c>
       <c r="B540" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C540">
         <v>9</v>
@@ -14476,7 +14476,7 @@
         <v>27281</v>
       </c>
       <c r="B541" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C541">
         <v>9</v>
@@ -14502,7 +14502,7 @@
         <v>27282</v>
       </c>
       <c r="B542" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C542">
         <v>10</v>
@@ -14528,7 +14528,7 @@
         <v>27283</v>
       </c>
       <c r="B543" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C543">
         <v>10</v>
@@ -14554,7 +14554,7 @@
         <v>27284</v>
       </c>
       <c r="B544" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C544">
         <v>10</v>
@@ -14580,7 +14580,7 @@
         <v>27285</v>
       </c>
       <c r="B545" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C545">
         <v>10</v>
@@ -14606,7 +14606,7 @@
         <v>27286</v>
       </c>
       <c r="B546" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C546">
         <v>10</v>
@@ -14632,7 +14632,7 @@
         <v>27287</v>
       </c>
       <c r="B547" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C547">
         <v>11</v>
@@ -14658,7 +14658,7 @@
         <v>27288</v>
       </c>
       <c r="B548" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C548">
         <v>11</v>
@@ -14684,7 +14684,7 @@
         <v>27289</v>
       </c>
       <c r="B549" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C549">
         <v>11</v>
@@ -14710,7 +14710,7 @@
         <v>27290</v>
       </c>
       <c r="B550" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C550">
         <v>11</v>
@@ -14736,7 +14736,7 @@
         <v>27291</v>
       </c>
       <c r="B551" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C551">
         <v>11</v>
@@ -14762,7 +14762,7 @@
         <v>27292</v>
       </c>
       <c r="B552" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C552">
         <v>11</v>
@@ -14788,7 +14788,7 @@
         <v>27293</v>
       </c>
       <c r="B553" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C553">
         <v>12</v>
@@ -14814,7 +14814,7 @@
         <v>27294</v>
       </c>
       <c r="B554" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C554">
         <v>12</v>
@@ -14840,7 +14840,7 @@
         <v>27295</v>
       </c>
       <c r="B555" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C555">
         <v>12</v>
@@ -14866,7 +14866,7 @@
         <v>27296</v>
       </c>
       <c r="B556" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C556">
         <v>12</v>
@@ -14892,7 +14892,7 @@
         <v>27297</v>
       </c>
       <c r="B557" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C557">
         <v>13</v>
@@ -14918,7 +14918,7 @@
         <v>27298</v>
       </c>
       <c r="B558" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C558">
         <v>13</v>
@@ -14944,7 +14944,7 @@
         <v>27299</v>
       </c>
       <c r="B559" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C559">
         <v>13</v>
@@ -14970,7 +14970,7 @@
         <v>27300</v>
       </c>
       <c r="B560" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C560">
         <v>13</v>
@@ -14996,7 +14996,7 @@
         <v>27301</v>
       </c>
       <c r="B561" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C561">
         <v>13</v>
@@ -15022,7 +15022,7 @@
         <v>27302</v>
       </c>
       <c r="B562" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C562">
         <v>14</v>
@@ -15048,7 +15048,7 @@
         <v>27303</v>
       </c>
       <c r="B563" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C563">
         <v>14</v>
@@ -15074,7 +15074,7 @@
         <v>27304</v>
       </c>
       <c r="B564" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C564">
         <v>14</v>
@@ -15100,7 +15100,7 @@
         <v>27305</v>
       </c>
       <c r="B565" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C565">
         <v>14</v>
@@ -15126,7 +15126,7 @@
         <v>27306</v>
       </c>
       <c r="B566" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C566">
         <v>15</v>
@@ -15152,7 +15152,7 @@
         <v>27307</v>
       </c>
       <c r="B567" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C567">
         <v>15</v>
@@ -15178,7 +15178,7 @@
         <v>27308</v>
       </c>
       <c r="B568" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C568">
         <v>15</v>
@@ -15204,7 +15204,7 @@
         <v>27309</v>
       </c>
       <c r="B569" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C569">
         <v>15</v>
@@ -15230,7 +15230,7 @@
         <v>27310</v>
       </c>
       <c r="B570" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C570">
         <v>15</v>
@@ -15256,7 +15256,7 @@
         <v>27311</v>
       </c>
       <c r="B571" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C571">
         <v>16</v>
@@ -15282,7 +15282,7 @@
         <v>27312</v>
       </c>
       <c r="B572" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C572">
         <v>16</v>
@@ -15308,7 +15308,7 @@
         <v>27313</v>
       </c>
       <c r="B573" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C573">
         <v>16</v>
@@ -15334,7 +15334,7 @@
         <v>27314</v>
       </c>
       <c r="B574" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C574">
         <v>16</v>
@@ -15360,7 +15360,7 @@
         <v>27315</v>
       </c>
       <c r="B575" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C575">
         <v>17</v>
@@ -15386,7 +15386,7 @@
         <v>27316</v>
       </c>
       <c r="B576" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C576">
         <v>17</v>
@@ -15412,7 +15412,7 @@
         <v>27317</v>
       </c>
       <c r="B577" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C577">
         <v>17</v>
@@ -15438,7 +15438,7 @@
         <v>27318</v>
       </c>
       <c r="B578" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C578">
         <v>17</v>
@@ -15464,7 +15464,7 @@
         <v>27319</v>
       </c>
       <c r="B579" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C579">
         <v>17</v>
@@ -15490,7 +15490,7 @@
         <v>27320</v>
       </c>
       <c r="B580" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C580">
         <v>18</v>
@@ -15516,7 +15516,7 @@
         <v>27321</v>
       </c>
       <c r="B581" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C581">
         <v>18</v>
@@ -15542,7 +15542,7 @@
         <v>27322</v>
       </c>
       <c r="B582" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C582">
         <v>18</v>
@@ -15568,7 +15568,7 @@
         <v>27323</v>
       </c>
       <c r="B583" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C583">
         <v>18</v>
@@ -15594,7 +15594,7 @@
         <v>27324</v>
       </c>
       <c r="B584" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C584">
         <v>18</v>
@@ -15620,7 +15620,7 @@
         <v>27325</v>
       </c>
       <c r="B585" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C585">
         <v>19</v>
@@ -15646,7 +15646,7 @@
         <v>27326</v>
       </c>
       <c r="B586" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C586">
         <v>19</v>
@@ -15672,7 +15672,7 @@
         <v>27327</v>
       </c>
       <c r="B587" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C587">
         <v>19</v>
@@ -15698,7 +15698,7 @@
         <v>27328</v>
       </c>
       <c r="B588" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C588">
         <v>19</v>
@@ -15724,7 +15724,7 @@
         <v>27329</v>
       </c>
       <c r="B589" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C589">
         <v>19</v>
@@ -15750,7 +15750,7 @@
         <v>27330</v>
       </c>
       <c r="B590" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C590">
         <v>19</v>
@@ -15776,7 +15776,7 @@
         <v>27331</v>
       </c>
       <c r="B591" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C591">
         <v>20</v>
@@ -15802,7 +15802,7 @@
         <v>27332</v>
       </c>
       <c r="B592" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C592">
         <v>20</v>
@@ -15828,7 +15828,7 @@
         <v>27333</v>
       </c>
       <c r="B593" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C593">
         <v>20</v>
@@ -15854,7 +15854,7 @@
         <v>27334</v>
       </c>
       <c r="B594" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C594">
         <v>20</v>
@@ -15880,7 +15880,7 @@
         <v>27335</v>
       </c>
       <c r="B595" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C595">
         <v>20</v>
@@ -15906,7 +15906,7 @@
         <v>27336</v>
       </c>
       <c r="B596" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C596">
         <v>21</v>
@@ -15932,7 +15932,7 @@
         <v>27337</v>
       </c>
       <c r="B597" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C597">
         <v>21</v>
@@ -15958,7 +15958,7 @@
         <v>27338</v>
       </c>
       <c r="B598" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C598">
         <v>21</v>
@@ -15981,7 +15981,7 @@
         <v>27339</v>
       </c>
       <c r="B599" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C599">
         <v>21</v>
@@ -16007,7 +16007,7 @@
         <v>27340</v>
       </c>
       <c r="B600" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C600">
         <v>21</v>
@@ -16033,7 +16033,7 @@
         <v>27341</v>
       </c>
       <c r="B601" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C601">
         <v>22</v>
@@ -16059,7 +16059,7 @@
         <v>27342</v>
       </c>
       <c r="B602" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C602">
         <v>22</v>
@@ -16085,7 +16085,7 @@
         <v>27343</v>
       </c>
       <c r="B603" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C603">
         <v>22</v>
@@ -16111,7 +16111,7 @@
         <v>27344</v>
       </c>
       <c r="B604" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C604">
         <v>22</v>
@@ -16137,7 +16137,7 @@
         <v>27345</v>
       </c>
       <c r="B605" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C605">
         <v>22</v>
@@ -16163,7 +16163,7 @@
         <v>27346</v>
       </c>
       <c r="B606" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C606">
         <v>23</v>
@@ -16189,7 +16189,7 @@
         <v>27347</v>
       </c>
       <c r="B607" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C607">
         <v>23</v>
@@ -16215,7 +16215,7 @@
         <v>27348</v>
       </c>
       <c r="B608" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C608">
         <v>23</v>
@@ -16241,7 +16241,7 @@
         <v>27349</v>
       </c>
       <c r="B609" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C609">
         <v>23</v>
@@ -16267,7 +16267,7 @@
         <v>27350</v>
       </c>
       <c r="B610" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C610">
         <v>23</v>
@@ -16293,7 +16293,7 @@
         <v>27351</v>
       </c>
       <c r="B611" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C611">
         <v>24</v>
@@ -16319,7 +16319,7 @@
         <v>27352</v>
       </c>
       <c r="B612" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C612">
         <v>24</v>
@@ -16345,7 +16345,7 @@
         <v>27353</v>
       </c>
       <c r="B613" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C613">
         <v>24</v>
@@ -16371,7 +16371,7 @@
         <v>27354</v>
       </c>
       <c r="B614" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C614">
         <v>24</v>
@@ -16397,7 +16397,7 @@
         <v>27355</v>
       </c>
       <c r="B615" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C615">
         <v>24</v>
@@ -16423,7 +16423,7 @@
         <v>27356</v>
       </c>
       <c r="B616" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C616">
         <v>25</v>
@@ -16449,7 +16449,7 @@
         <v>27357</v>
       </c>
       <c r="B617" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C617">
         <v>25</v>
@@ -16475,7 +16475,7 @@
         <v>27358</v>
       </c>
       <c r="B618" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C618">
         <v>25</v>
@@ -16501,7 +16501,7 @@
         <v>27359</v>
       </c>
       <c r="B619" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C619">
         <v>25</v>
@@ -16527,7 +16527,7 @@
         <v>27360</v>
       </c>
       <c r="B620" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C620">
         <v>25</v>
@@ -16553,7 +16553,7 @@
         <v>27361</v>
       </c>
       <c r="B621" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C621">
         <v>26</v>
@@ -16579,7 +16579,7 @@
         <v>27362</v>
       </c>
       <c r="B622" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C622">
         <v>26</v>
@@ -16605,7 +16605,7 @@
         <v>27363</v>
       </c>
       <c r="B623" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C623">
         <v>26</v>
@@ -16631,7 +16631,7 @@
         <v>27364</v>
       </c>
       <c r="B624" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C624">
         <v>26</v>
@@ -16657,7 +16657,7 @@
         <v>27365</v>
       </c>
       <c r="B625" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C625">
         <v>26</v>
@@ -16683,7 +16683,7 @@
         <v>27366</v>
       </c>
       <c r="B626" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C626">
         <v>27</v>
@@ -16709,7 +16709,7 @@
         <v>27367</v>
       </c>
       <c r="B627" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C627">
         <v>27</v>
@@ -16735,7 +16735,7 @@
         <v>27368</v>
       </c>
       <c r="B628" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C628">
         <v>27</v>
@@ -16761,7 +16761,7 @@
         <v>27369</v>
       </c>
       <c r="B629" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C629">
         <v>27</v>
@@ -16787,7 +16787,7 @@
         <v>27370</v>
       </c>
       <c r="B630" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C630">
         <v>27</v>
@@ -16797,6 +16797,9 @@
       </c>
       <c r="E630">
         <v>0</v>
+      </c>
+      <c r="F630">
+        <v>0.8</v>
       </c>
       <c r="G630">
         <v>2.7</v>
@@ -16810,7 +16813,7 @@
         <v>27371</v>
       </c>
       <c r="B631" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C631">
         <v>27</v>
@@ -16820,6 +16823,9 @@
       </c>
       <c r="E631">
         <v>0</v>
+      </c>
+      <c r="F631">
+        <v>0.55000000000000004</v>
       </c>
       <c r="G631">
         <v>3.5</v>
@@ -16833,7 +16839,7 @@
         <v>27372</v>
       </c>
       <c r="B632" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C632">
         <v>28</v>
@@ -16843,6 +16849,9 @@
       </c>
       <c r="E632">
         <v>0</v>
+      </c>
+      <c r="F632">
+        <v>0.4</v>
       </c>
       <c r="G632">
         <v>2.9</v>
@@ -16856,7 +16865,7 @@
         <v>27373</v>
       </c>
       <c r="B633" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C633">
         <v>28</v>
@@ -16866,6 +16875,9 @@
       </c>
       <c r="E633">
         <v>0</v>
+      </c>
+      <c r="F633">
+        <v>0.75</v>
       </c>
       <c r="G633">
         <v>2.7</v>
@@ -16879,7 +16891,7 @@
         <v>27374</v>
       </c>
       <c r="B634" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C634">
         <v>28</v>
@@ -16889,6 +16901,9 @@
       </c>
       <c r="E634">
         <v>0</v>
+      </c>
+      <c r="F634">
+        <v>0.65</v>
       </c>
       <c r="G634">
         <v>2.9</v>
@@ -16902,7 +16917,7 @@
         <v>27375</v>
       </c>
       <c r="B635" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C635">
         <v>28</v>
@@ -16912,6 +16927,9 @@
       </c>
       <c r="E635">
         <v>30</v>
+      </c>
+      <c r="F635">
+        <v>0.55000000000000004</v>
       </c>
       <c r="G635">
         <v>1.9</v>
@@ -16925,7 +16943,7 @@
         <v>27376</v>
       </c>
       <c r="B636" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C636">
         <v>28</v>
@@ -16935,6 +16953,9 @@
       </c>
       <c r="E636">
         <v>0</v>
+      </c>
+      <c r="F636">
+        <v>0.65</v>
       </c>
       <c r="G636">
         <v>2.78</v>
@@ -16948,7 +16969,7 @@
         <v>27377</v>
       </c>
       <c r="B637" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C637">
         <v>29</v>
@@ -16958,6 +16979,9 @@
       </c>
       <c r="E637">
         <v>0</v>
+      </c>
+      <c r="F637">
+        <v>0.4</v>
       </c>
       <c r="G637">
         <v>1.6</v>
@@ -16971,7 +16995,7 @@
         <v>27378</v>
       </c>
       <c r="B638" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C638">
         <v>29</v>
@@ -16981,6 +17005,9 @@
       </c>
       <c r="E638">
         <v>0</v>
+      </c>
+      <c r="F638">
+        <v>0.55000000000000004</v>
       </c>
       <c r="G638">
         <v>1.9</v>
@@ -16994,7 +17021,7 @@
         <v>27379</v>
       </c>
       <c r="B639" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C639">
         <v>29</v>
@@ -17004,6 +17031,9 @@
       </c>
       <c r="E639">
         <v>0</v>
+      </c>
+      <c r="F639">
+        <v>0.5</v>
       </c>
       <c r="G639">
         <v>2.1</v>
@@ -17017,7 +17047,7 @@
         <v>27380</v>
       </c>
       <c r="B640" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C640">
         <v>29</v>
@@ -17027,6 +17057,9 @@
       </c>
       <c r="E640">
         <v>0</v>
+      </c>
+      <c r="F640">
+        <v>0.5</v>
       </c>
       <c r="G640">
         <v>2</v>
@@ -17040,7 +17073,7 @@
         <v>27381</v>
       </c>
       <c r="B641" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C641">
         <v>29</v>
@@ -17050,6 +17083,9 @@
       </c>
       <c r="E641">
         <v>0</v>
+      </c>
+      <c r="F641">
+        <v>0.55000000000000004</v>
       </c>
       <c r="G641">
         <v>1.6</v>
@@ -17063,7 +17099,7 @@
         <v>27382</v>
       </c>
       <c r="B642" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C642">
         <v>30</v>
@@ -17073,6 +17109,9 @@
       </c>
       <c r="E642">
         <v>15</v>
+      </c>
+      <c r="F642">
+        <v>0.6</v>
       </c>
       <c r="G642">
         <v>0.8</v>
@@ -17086,7 +17125,7 @@
         <v>27383</v>
       </c>
       <c r="B643" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C643">
         <v>30</v>
@@ -17097,8 +17136,14 @@
       <c r="E643">
         <v>0</v>
       </c>
+      <c r="F643">
+        <v>0.4</v>
+      </c>
       <c r="G643">
         <v>0.6</v>
+      </c>
+      <c r="H643">
+        <v>1.2</v>
       </c>
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.35">
@@ -17106,7 +17151,7 @@
         <v>27384</v>
       </c>
       <c r="B644" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C644">
         <v>30</v>
@@ -17117,8 +17162,14 @@
       <c r="E644">
         <v>27</v>
       </c>
+      <c r="F644">
+        <v>0.65</v>
+      </c>
       <c r="G644">
         <v>1</v>
+      </c>
+      <c r="H644">
+        <v>2</v>
       </c>
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.35">
@@ -17126,7 +17177,7 @@
         <v>27385</v>
       </c>
       <c r="B645" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C645">
         <v>30</v>
@@ -17137,8 +17188,14 @@
       <c r="E645">
         <v>0</v>
       </c>
+      <c r="F645">
+        <v>0.6</v>
+      </c>
       <c r="G645">
         <v>0.8</v>
+      </c>
+      <c r="H645">
+        <v>1.9</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.35">
@@ -17146,7 +17203,7 @@
         <v>27386</v>
       </c>
       <c r="B646" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C646">
         <v>30</v>
@@ -17157,8 +17214,14 @@
       <c r="E646">
         <v>24</v>
       </c>
+      <c r="F646">
+        <v>0.6</v>
+      </c>
       <c r="G646">
         <v>0.7</v>
+      </c>
+      <c r="H646">
+        <v>1.6</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.35">
@@ -17166,7 +17229,7 @@
         <v>27387</v>
       </c>
       <c r="B647" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C647">
         <v>1</v>
@@ -17177,8 +17240,14 @@
       <c r="E647">
         <v>0</v>
       </c>
+      <c r="F647">
+        <v>0.65</v>
+      </c>
       <c r="G647">
         <v>0.5</v>
+      </c>
+      <c r="H647">
+        <v>1.6</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.35">
@@ -17186,7 +17255,7 @@
         <v>27388</v>
       </c>
       <c r="B648" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C648">
         <v>1</v>
@@ -17197,8 +17266,14 @@
       <c r="E648">
         <v>24</v>
       </c>
+      <c r="F648">
+        <v>0.6</v>
+      </c>
       <c r="G648">
         <v>0.6</v>
+      </c>
+      <c r="H648">
+        <v>2</v>
       </c>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.35">
@@ -17206,7 +17281,7 @@
         <v>27389</v>
       </c>
       <c r="B649" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C649">
         <v>1</v>
@@ -17217,8 +17292,14 @@
       <c r="E649">
         <v>0</v>
       </c>
+      <c r="F649">
+        <v>0.8</v>
+      </c>
       <c r="G649">
         <v>0.9</v>
+      </c>
+      <c r="H649">
+        <v>2.1</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.35">
@@ -17226,7 +17307,7 @@
         <v>27390</v>
       </c>
       <c r="B650" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C650">
         <v>1</v>
@@ -17237,8 +17318,14 @@
       <c r="E650">
         <v>0</v>
       </c>
+      <c r="F650">
+        <v>0.65</v>
+      </c>
       <c r="G650">
         <v>2.7</v>
+      </c>
+      <c r="H650">
+        <v>1.2</v>
       </c>
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.35">
@@ -17246,7 +17333,7 @@
         <v>27391</v>
       </c>
       <c r="B651" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C651">
         <v>2</v>
@@ -17257,8 +17344,14 @@
       <c r="E651">
         <v>0</v>
       </c>
+      <c r="F651">
+        <v>0.7</v>
+      </c>
       <c r="G651">
         <v>2.4</v>
+      </c>
+      <c r="H651">
+        <v>1.4</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.35">
@@ -17266,7 +17359,7 @@
         <v>27392</v>
       </c>
       <c r="B652" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C652">
         <v>2</v>
@@ -17277,8 +17370,14 @@
       <c r="E652">
         <v>0</v>
       </c>
+      <c r="F652">
+        <v>0.6</v>
+      </c>
       <c r="G652">
         <v>2.6</v>
+      </c>
+      <c r="H652">
+        <v>1.5</v>
       </c>
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.35">
@@ -17286,7 +17385,7 @@
         <v>27393</v>
       </c>
       <c r="B653" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C653">
         <v>2</v>
@@ -17297,8 +17396,14 @@
       <c r="E653">
         <v>0</v>
       </c>
+      <c r="F653">
+        <v>0.75</v>
+      </c>
       <c r="G653">
         <v>2.7</v>
+      </c>
+      <c r="H653">
+        <v>1.3</v>
       </c>
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.35">
@@ -17306,7 +17411,7 @@
         <v>27394</v>
       </c>
       <c r="B654" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C654">
         <v>2</v>
@@ -17317,8 +17422,14 @@
       <c r="E654">
         <v>0</v>
       </c>
+      <c r="F654">
+        <v>0.8</v>
+      </c>
       <c r="G654">
         <v>2.2999999999999998</v>
+      </c>
+      <c r="H654">
+        <v>1.5</v>
       </c>
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.35">
@@ -17326,7 +17437,7 @@
         <v>27395</v>
       </c>
       <c r="B655" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C655">
         <v>2</v>
@@ -17337,8 +17448,14 @@
       <c r="E655">
         <v>0</v>
       </c>
+      <c r="F655">
+        <v>0.7</v>
+      </c>
       <c r="G655">
         <v>1.6</v>
+      </c>
+      <c r="H655">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.35">
@@ -17346,7 +17463,7 @@
         <v>27396</v>
       </c>
       <c r="B656" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C656">
         <v>3</v>
@@ -17357,16 +17474,22 @@
       <c r="E656">
         <v>0</v>
       </c>
+      <c r="F656">
+        <v>0.75</v>
+      </c>
       <c r="G656">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H656">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A657">
         <v>27397</v>
       </c>
       <c r="B657" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C657">
         <v>3</v>
@@ -17377,16 +17500,22 @@
       <c r="E657">
         <v>8</v>
       </c>
+      <c r="F657">
+        <v>0.8</v>
+      </c>
       <c r="G657">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H657">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A658">
         <v>27398</v>
       </c>
       <c r="B658" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C658">
         <v>3</v>
@@ -17397,212 +17526,1567 @@
       <c r="E658">
         <v>0</v>
       </c>
+      <c r="F658">
+        <v>0.9</v>
+      </c>
       <c r="G658">
         <v>4.9000000000000004</v>
       </c>
-    </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H658">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="659" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A659">
         <v>27399</v>
       </c>
       <c r="B659" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C659">
         <v>3</v>
       </c>
       <c r="D659">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E659">
         <v>0</v>
       </c>
+      <c r="F659">
+        <v>0.75</v>
+      </c>
       <c r="G659">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2.7</v>
+      </c>
+      <c r="H659">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="660" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A660">
         <v>27400</v>
       </c>
       <c r="B660" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C660">
         <v>3</v>
       </c>
       <c r="D660">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E660">
         <v>0</v>
       </c>
+      <c r="F660">
+        <v>0.6</v>
+      </c>
       <c r="G660">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.35">
+        <v>3.5</v>
+      </c>
+      <c r="H660">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="661" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A661">
         <v>27401</v>
       </c>
       <c r="B661" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C661">
         <v>4</v>
       </c>
       <c r="D661">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E661">
         <v>0</v>
       </c>
+      <c r="F661">
+        <v>0.75</v>
+      </c>
       <c r="G661">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.35">
+        <v>3.1</v>
+      </c>
+      <c r="H661">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="662" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A662">
         <v>27402</v>
       </c>
       <c r="B662" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C662">
         <v>4</v>
       </c>
       <c r="D662">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E662">
         <v>0</v>
       </c>
+      <c r="F662">
+        <v>0.8</v>
+      </c>
       <c r="G662">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2.9</v>
+      </c>
+      <c r="H662">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="663" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A663">
         <v>27403</v>
       </c>
       <c r="B663" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C663">
         <v>4</v>
       </c>
       <c r="D663">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E663">
         <v>0</v>
       </c>
+      <c r="F663">
+        <v>0.9</v>
+      </c>
       <c r="G663">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2.7</v>
+      </c>
+      <c r="H663">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="664" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A664">
         <v>27404</v>
       </c>
       <c r="B664" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C664">
         <v>4</v>
       </c>
       <c r="D664">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E664">
         <v>0</v>
       </c>
+      <c r="F664">
+        <v>0.85</v>
+      </c>
       <c r="G664">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.35">
+        <v>3.1</v>
+      </c>
+      <c r="H664">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="665" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A665">
         <v>27405</v>
       </c>
       <c r="B665" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C665">
         <v>4</v>
       </c>
       <c r="D665">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E665">
         <v>0</v>
       </c>
+      <c r="F665">
+        <v>4.3499999999999996</v>
+      </c>
       <c r="G665">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.35">
+        <v>3.4</v>
+      </c>
+      <c r="H665">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="666" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A666">
         <v>27406</v>
       </c>
       <c r="B666" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C666">
         <v>5</v>
       </c>
       <c r="D666">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E666">
         <v>0</v>
       </c>
+      <c r="F666">
+        <v>0.85</v>
+      </c>
       <c r="G666">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.35">
+        <v>3.5</v>
+      </c>
+      <c r="H666">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="667" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A667">
         <v>27407</v>
       </c>
       <c r="B667" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C667">
         <v>5</v>
       </c>
       <c r="D667">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E667">
         <v>0</v>
       </c>
+      <c r="F667">
+        <v>0.8</v>
+      </c>
       <c r="G667">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2.9</v>
+      </c>
+      <c r="H667">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="668" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A668">
         <v>27408</v>
       </c>
       <c r="B668" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C668">
         <v>5</v>
       </c>
       <c r="D668">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E668">
         <v>0</v>
       </c>
+      <c r="F668">
+        <v>0.6</v>
+      </c>
       <c r="G668">
+        <v>3.3</v>
+      </c>
+      <c r="H668">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="669" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A669">
+        <v>27409</v>
+      </c>
+      <c r="B669" t="s">
+        <v>13</v>
+      </c>
+      <c r="C669">
+        <v>5</v>
+      </c>
+      <c r="D669">
+        <v>94</v>
+      </c>
+      <c r="E669">
+        <v>0</v>
+      </c>
+      <c r="F669">
+        <v>0.4</v>
+      </c>
+      <c r="G669">
+        <v>3.6</v>
+      </c>
+      <c r="H669">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="670" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A670">
+        <v>27410</v>
+      </c>
+      <c r="B670" t="s">
+        <v>13</v>
+      </c>
+      <c r="C670">
+        <v>5</v>
+      </c>
+      <c r="D670">
+        <v>74</v>
+      </c>
+      <c r="E670">
+        <v>0</v>
+      </c>
+      <c r="F670">
+        <v>0.65</v>
+      </c>
+      <c r="G670">
+        <v>3.2</v>
+      </c>
+      <c r="H670">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="671" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A671">
+        <v>27411</v>
+      </c>
+      <c r="B671" t="s">
+        <v>13</v>
+      </c>
+      <c r="C671">
+        <v>6</v>
+      </c>
+      <c r="D671">
+        <v>96</v>
+      </c>
+      <c r="E671">
+        <v>0</v>
+      </c>
+      <c r="F671">
+        <v>0.7</v>
+      </c>
+      <c r="G671">
+        <v>3.4</v>
+      </c>
+      <c r="H671">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="672" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A672">
+        <v>27412</v>
+      </c>
+      <c r="B672" t="s">
+        <v>13</v>
+      </c>
+      <c r="C672">
+        <v>6</v>
+      </c>
+      <c r="D672">
+        <v>98</v>
+      </c>
+      <c r="E672">
+        <v>0</v>
+      </c>
+      <c r="F672">
+        <v>0.75</v>
+      </c>
+      <c r="G672">
+        <v>3</v>
+      </c>
+      <c r="H672">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="673" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A673">
+        <v>27413</v>
+      </c>
+      <c r="B673" t="s">
+        <v>13</v>
+      </c>
+      <c r="C673">
+        <v>6</v>
+      </c>
+      <c r="D673">
+        <v>88</v>
+      </c>
+      <c r="E673">
+        <v>0</v>
+      </c>
+      <c r="F673">
+        <v>0.8</v>
+      </c>
+      <c r="G673">
+        <v>2.5</v>
+      </c>
+      <c r="H673">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A674">
+        <v>27414</v>
+      </c>
+      <c r="B674" t="s">
+        <v>13</v>
+      </c>
+      <c r="C674">
+        <v>6</v>
+      </c>
+      <c r="D674">
+        <v>73</v>
+      </c>
+      <c r="E674">
+        <v>0</v>
+      </c>
+      <c r="F674">
+        <v>0.7</v>
+      </c>
+      <c r="G674">
+        <v>3.5</v>
+      </c>
+      <c r="H674">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A675">
+        <v>27415</v>
+      </c>
+      <c r="B675" t="s">
+        <v>13</v>
+      </c>
+      <c r="C675">
+        <v>6</v>
+      </c>
+      <c r="D675">
+        <v>80</v>
+      </c>
+      <c r="E675">
+        <v>0</v>
+      </c>
+      <c r="F675">
+        <v>0.5</v>
+      </c>
+      <c r="G675">
+        <v>3.4</v>
+      </c>
+      <c r="H675">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A676">
+        <v>27416</v>
+      </c>
+      <c r="B676" t="s">
+        <v>13</v>
+      </c>
+      <c r="C676">
+        <v>7</v>
+      </c>
+      <c r="D676">
+        <v>90</v>
+      </c>
+      <c r="E676">
+        <v>0</v>
+      </c>
+      <c r="F676">
+        <v>0.65</v>
+      </c>
+      <c r="G676">
+        <v>3.7</v>
+      </c>
+      <c r="H676">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A677">
+        <v>27417</v>
+      </c>
+      <c r="B677" t="s">
+        <v>13</v>
+      </c>
+      <c r="C677">
+        <v>7</v>
+      </c>
+      <c r="D677">
+        <v>86</v>
+      </c>
+      <c r="E677">
+        <v>0</v>
+      </c>
+      <c r="F677">
+        <v>0.7</v>
+      </c>
+      <c r="G677">
+        <v>3</v>
+      </c>
+      <c r="H677">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A678">
+        <v>27418</v>
+      </c>
+      <c r="B678" t="s">
+        <v>13</v>
+      </c>
+      <c r="C678">
+        <v>7</v>
+      </c>
+      <c r="D678">
+        <v>95</v>
+      </c>
+      <c r="E678">
+        <v>0</v>
+      </c>
+      <c r="F678">
+        <v>0.75</v>
+      </c>
+      <c r="G678">
+        <v>3.4</v>
+      </c>
+      <c r="H678">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A679">
+        <v>27419</v>
+      </c>
+      <c r="B679" t="s">
+        <v>13</v>
+      </c>
+      <c r="C679">
+        <v>7</v>
+      </c>
+      <c r="D679">
+        <v>95</v>
+      </c>
+      <c r="E679">
+        <v>0</v>
+      </c>
+      <c r="F679">
+        <v>0.4</v>
+      </c>
+      <c r="G679">
+        <v>3.1</v>
+      </c>
+      <c r="H679">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A680">
+        <v>27420</v>
+      </c>
+      <c r="B680" t="s">
+        <v>13</v>
+      </c>
+      <c r="C680">
+        <v>7</v>
+      </c>
+      <c r="D680">
+        <v>80</v>
+      </c>
+      <c r="E680">
+        <v>0</v>
+      </c>
+      <c r="F680">
+        <v>0.6</v>
+      </c>
+      <c r="G680">
+        <v>3.4</v>
+      </c>
+      <c r="H680">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A681">
+        <v>27421</v>
+      </c>
+      <c r="B681" t="s">
+        <v>13</v>
+      </c>
+      <c r="C681">
+        <v>8</v>
+      </c>
+      <c r="D681">
+        <v>83</v>
+      </c>
+      <c r="E681">
+        <v>0</v>
+      </c>
+      <c r="G681">
+        <v>4</v>
+      </c>
+      <c r="H681">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A682">
+        <v>27422</v>
+      </c>
+      <c r="B682" t="s">
+        <v>13</v>
+      </c>
+      <c r="C682">
+        <v>8</v>
+      </c>
+      <c r="D682">
+        <v>85</v>
+      </c>
+      <c r="E682">
+        <v>0</v>
+      </c>
+      <c r="G682">
+        <v>3.8</v>
+      </c>
+      <c r="H682">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A683">
+        <v>27423</v>
+      </c>
+      <c r="B683" t="s">
+        <v>13</v>
+      </c>
+      <c r="C683">
+        <v>8</v>
+      </c>
+      <c r="D683">
+        <v>135</v>
+      </c>
+      <c r="E683">
+        <v>0</v>
+      </c>
+      <c r="G683">
+        <v>3.5</v>
+      </c>
+      <c r="H683">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A684">
+        <v>27424</v>
+      </c>
+      <c r="B684" t="s">
+        <v>13</v>
+      </c>
+      <c r="C684">
+        <v>8</v>
+      </c>
+      <c r="D684">
+        <v>94</v>
+      </c>
+      <c r="E684">
+        <v>0</v>
+      </c>
+      <c r="G684">
+        <v>3.7</v>
+      </c>
+      <c r="H684">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A685">
+        <v>27425</v>
+      </c>
+      <c r="B685" t="s">
+        <v>13</v>
+      </c>
+      <c r="C685">
+        <v>8</v>
+      </c>
+      <c r="D685">
+        <v>116</v>
+      </c>
+      <c r="E685">
+        <v>0</v>
+      </c>
+      <c r="G685">
+        <v>3.51</v>
+      </c>
+      <c r="H685">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A686">
+        <v>27426</v>
+      </c>
+      <c r="B686" t="s">
+        <v>13</v>
+      </c>
+      <c r="C686">
+        <v>9</v>
+      </c>
+      <c r="D686">
+        <v>74</v>
+      </c>
+      <c r="E686">
+        <v>0</v>
+      </c>
+      <c r="G686">
+        <v>5</v>
+      </c>
+      <c r="H686">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A687">
+        <v>27427</v>
+      </c>
+      <c r="B687" t="s">
+        <v>13</v>
+      </c>
+      <c r="C687">
+        <v>9</v>
+      </c>
+      <c r="D687">
+        <v>80</v>
+      </c>
+      <c r="E687">
+        <v>0</v>
+      </c>
+      <c r="G687">
+        <v>4.8</v>
+      </c>
+      <c r="H687">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A688">
+        <v>27428</v>
+      </c>
+      <c r="B688" t="s">
+        <v>13</v>
+      </c>
+      <c r="C688">
+        <v>9</v>
+      </c>
+      <c r="D688">
+        <v>77</v>
+      </c>
+      <c r="E688">
+        <v>0</v>
+      </c>
+      <c r="G688">
+        <v>3.8</v>
+      </c>
+      <c r="H688">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="689" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A689">
+        <v>27429</v>
+      </c>
+      <c r="B689" t="s">
+        <v>13</v>
+      </c>
+      <c r="C689">
+        <v>9</v>
+      </c>
+      <c r="D689">
+        <v>81</v>
+      </c>
+      <c r="E689">
+        <v>0</v>
+      </c>
+      <c r="G689">
+        <v>3.5</v>
+      </c>
+      <c r="H689">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="690" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A690">
+        <v>27430</v>
+      </c>
+      <c r="B690" t="s">
+        <v>13</v>
+      </c>
+      <c r="C690">
+        <v>9</v>
+      </c>
+      <c r="D690">
+        <v>100</v>
+      </c>
+      <c r="E690">
+        <v>0</v>
+      </c>
+      <c r="G690">
+        <v>3.8</v>
+      </c>
+      <c r="H690">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="691" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A691">
+        <v>27431</v>
+      </c>
+      <c r="B691" t="s">
+        <v>13</v>
+      </c>
+      <c r="C691">
+        <v>10</v>
+      </c>
+      <c r="D691">
+        <v>110</v>
+      </c>
+      <c r="E691">
+        <v>0</v>
+      </c>
+      <c r="G691">
+        <v>3.6</v>
+      </c>
+      <c r="H691">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="692" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A692">
+        <v>27432</v>
+      </c>
+      <c r="B692" t="s">
+        <v>13</v>
+      </c>
+      <c r="C692">
+        <v>10</v>
+      </c>
+      <c r="D692">
+        <v>73</v>
+      </c>
+      <c r="E692">
+        <v>0</v>
+      </c>
+      <c r="G692">
+        <v>3.9</v>
+      </c>
+      <c r="H692">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="693" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A693">
+        <v>27433</v>
+      </c>
+      <c r="B693" t="s">
+        <v>13</v>
+      </c>
+      <c r="C693">
+        <v>10</v>
+      </c>
+      <c r="D693">
+        <v>69</v>
+      </c>
+      <c r="E693">
+        <v>0</v>
+      </c>
+      <c r="G693">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H693">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="694" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A694">
+        <v>27434</v>
+      </c>
+      <c r="B694" t="s">
+        <v>13</v>
+      </c>
+      <c r="C694">
+        <v>10</v>
+      </c>
+      <c r="D694">
+        <v>89</v>
+      </c>
+      <c r="E694">
+        <v>0</v>
+      </c>
+      <c r="G694">
+        <v>3.1</v>
+      </c>
+      <c r="H694">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="695" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A695">
+        <v>27435</v>
+      </c>
+      <c r="B695" t="s">
+        <v>13</v>
+      </c>
+      <c r="C695">
+        <v>10</v>
+      </c>
+      <c r="D695">
+        <v>97</v>
+      </c>
+      <c r="E695">
+        <v>0</v>
+      </c>
+      <c r="G695">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="696" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A696">
+        <v>27436</v>
+      </c>
+      <c r="B696" t="s">
+        <v>13</v>
+      </c>
+      <c r="C696">
+        <v>10</v>
+      </c>
+      <c r="D696">
+        <v>82</v>
+      </c>
+      <c r="E696">
+        <v>0</v>
+      </c>
+      <c r="G696">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="697" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A697">
+        <v>27437</v>
+      </c>
+      <c r="B697" t="s">
+        <v>13</v>
+      </c>
+      <c r="C697">
+        <v>11</v>
+      </c>
+      <c r="D697">
+        <v>90</v>
+      </c>
+      <c r="E697">
+        <v>0</v>
+      </c>
+      <c r="G697">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="698" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A698">
+        <v>27438</v>
+      </c>
+      <c r="B698" t="s">
+        <v>13</v>
+      </c>
+      <c r="C698">
+        <v>11</v>
+      </c>
+      <c r="D698">
+        <v>99</v>
+      </c>
+      <c r="E698">
+        <v>0</v>
+      </c>
+      <c r="G698">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="699" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A699">
+        <v>27439</v>
+      </c>
+      <c r="B699" t="s">
+        <v>13</v>
+      </c>
+      <c r="C699">
+        <v>11</v>
+      </c>
+      <c r="D699">
+        <v>97</v>
+      </c>
+      <c r="E699">
+        <v>0</v>
+      </c>
+      <c r="G699">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="700" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A700">
+        <v>27440</v>
+      </c>
+      <c r="B700" t="s">
+        <v>13</v>
+      </c>
+      <c r="C700">
+        <v>11</v>
+      </c>
+      <c r="D700">
+        <v>90</v>
+      </c>
+      <c r="E700">
+        <v>0</v>
+      </c>
+      <c r="G700">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="701" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A701">
+        <v>27441</v>
+      </c>
+      <c r="B701" t="s">
+        <v>13</v>
+      </c>
+      <c r="C701">
+        <v>11</v>
+      </c>
+      <c r="D701">
+        <v>94</v>
+      </c>
+      <c r="E701">
+        <v>0</v>
+      </c>
+      <c r="G701">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="702" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A702">
+        <v>27442</v>
+      </c>
+      <c r="B702" t="s">
+        <v>13</v>
+      </c>
+      <c r="C702">
+        <v>12</v>
+      </c>
+      <c r="D702">
+        <v>90</v>
+      </c>
+      <c r="E702">
+        <v>0</v>
+      </c>
+      <c r="G702">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="703" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A703">
+        <v>27444</v>
+      </c>
+      <c r="B703" t="s">
+        <v>13</v>
+      </c>
+      <c r="C703">
+        <v>12</v>
+      </c>
+      <c r="D703">
+        <v>34</v>
+      </c>
+      <c r="E703">
+        <v>70</v>
+      </c>
+      <c r="G703">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="704" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A704">
+        <v>27445</v>
+      </c>
+      <c r="B704" t="s">
+        <v>13</v>
+      </c>
+      <c r="C704">
+        <v>12</v>
+      </c>
+      <c r="D704">
+        <v>80</v>
+      </c>
+      <c r="E704">
+        <v>27</v>
+      </c>
+      <c r="G704">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="705" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A705">
+        <v>27446</v>
+      </c>
+      <c r="B705" t="s">
+        <v>13</v>
+      </c>
+      <c r="C705">
+        <v>12</v>
+      </c>
+      <c r="D705">
+        <v>81</v>
+      </c>
+      <c r="E705">
+        <v>0</v>
+      </c>
+      <c r="G705">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="706" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A706">
+        <v>27447</v>
+      </c>
+      <c r="B706" t="s">
+        <v>13</v>
+      </c>
+      <c r="C706">
+        <v>12</v>
+      </c>
+      <c r="D706">
+        <v>3</v>
+      </c>
+      <c r="E706">
+        <v>99</v>
+      </c>
+      <c r="G706">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="707" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A707">
+        <v>27448</v>
+      </c>
+      <c r="B707" t="s">
+        <v>13</v>
+      </c>
+      <c r="C707">
+        <v>13</v>
+      </c>
+      <c r="D707">
+        <v>106</v>
+      </c>
+      <c r="E707">
+        <v>41</v>
+      </c>
+      <c r="G707">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="708" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A708">
+        <v>27449</v>
+      </c>
+      <c r="B708" t="s">
+        <v>13</v>
+      </c>
+      <c r="C708">
+        <v>13</v>
+      </c>
+      <c r="D708">
+        <v>29</v>
+      </c>
+      <c r="E708">
+        <v>76</v>
+      </c>
+      <c r="G708">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="709" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A709">
+        <v>27450</v>
+      </c>
+      <c r="B709" t="s">
+        <v>13</v>
+      </c>
+      <c r="C709">
+        <v>13</v>
+      </c>
+      <c r="D709">
+        <v>1</v>
+      </c>
+      <c r="E709">
+        <v>81</v>
+      </c>
+      <c r="G709">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="710" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A710">
+        <v>27451</v>
+      </c>
+      <c r="B710" t="s">
+        <v>13</v>
+      </c>
+      <c r="C710">
+        <v>13</v>
+      </c>
+      <c r="D710">
+        <v>106</v>
+      </c>
+      <c r="E710">
+        <v>18</v>
+      </c>
+      <c r="G710">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="711" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A711">
+        <v>27452</v>
+      </c>
+      <c r="B711" t="s">
+        <v>13</v>
+      </c>
+      <c r="C711">
+        <v>13</v>
+      </c>
+      <c r="D711">
+        <v>2</v>
+      </c>
+      <c r="E711">
+        <v>140</v>
+      </c>
+      <c r="G711">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="712" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A712">
+        <v>27453</v>
+      </c>
+      <c r="B712" t="s">
+        <v>13</v>
+      </c>
+      <c r="C712">
+        <v>14</v>
+      </c>
+      <c r="D712">
+        <v>10</v>
+      </c>
+      <c r="E712">
+        <v>144</v>
+      </c>
+      <c r="G712">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="713" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A713">
+        <v>27454</v>
+      </c>
+      <c r="B713" t="s">
+        <v>13</v>
+      </c>
+      <c r="C713">
+        <v>14</v>
+      </c>
+      <c r="D713">
+        <v>2</v>
+      </c>
+      <c r="E713">
+        <v>115</v>
+      </c>
+      <c r="G713">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="714" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A714">
+        <v>27455</v>
+      </c>
+      <c r="B714" t="s">
+        <v>13</v>
+      </c>
+      <c r="C714">
+        <v>14</v>
+      </c>
+      <c r="D714">
+        <v>0</v>
+      </c>
+      <c r="E714">
+        <v>124</v>
+      </c>
+      <c r="G714">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="715" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A715">
+        <v>27456</v>
+      </c>
+      <c r="B715" t="s">
+        <v>13</v>
+      </c>
+      <c r="C715">
+        <v>14</v>
+      </c>
+      <c r="D715">
+        <v>0</v>
+      </c>
+      <c r="E715">
+        <v>152</v>
+      </c>
+      <c r="G715">
         <v>2.9</v>
+      </c>
+    </row>
+    <row r="716" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A716">
+        <v>27457</v>
+      </c>
+      <c r="B716" t="s">
+        <v>13</v>
+      </c>
+      <c r="C716">
+        <v>15</v>
+      </c>
+      <c r="D716">
+        <v>0</v>
+      </c>
+      <c r="E716">
+        <v>99</v>
+      </c>
+      <c r="G716">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="717" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A717">
+        <v>27458</v>
+      </c>
+      <c r="B717" t="s">
+        <v>13</v>
+      </c>
+      <c r="C717">
+        <v>15</v>
+      </c>
+      <c r="D717">
+        <v>0</v>
+      </c>
+      <c r="E717">
+        <v>74</v>
+      </c>
+      <c r="G717">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E668" xr:uid="{6D6A4A6A-BD55-4AFD-8065-F1F24C71989F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DD20CFEBF900A640A684681316133414" ma:contentTypeVersion="3" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="9864a026faa20f7be52dcf0d5ab70640">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c81cef8d-56cf-4fb3-916d-cd9870b06c4e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3c344668b2c90b13ae1d26246829e49" ns2:_="">
+    <xsd:import namespace="c81cef8d-56cf-4fb3-916d-cd9870b06c4e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c81cef8d-56cf-4fb3-916d-cd9870b06c4e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C37DC91B-1FD1-462B-B6B6-20133FCEFCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{916BC0DA-DED6-4114-8B92-C68BA42E8CEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c81cef8d-56cf-4fb3-916d-cd9870b06c4e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{917E94CA-6AEE-424B-80DF-4EC2DE62C9E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c81cef8d-56cf-4fb3-916d-cd9870b06c4e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>